--- a/output_phyto/phyto_Intermediate_zhang_2013.xlsx
+++ b/output_phyto/phyto_Intermediate_zhang_2013.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
   <si>
     <t>NA</t>
   </si>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">10.1098/rsta.2013.0096</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_zhang_2013.xlsx</t>
+    <t xml:space="preserve">phytoplankton_zhang_2013_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
-    <t xml:space="preserve">alkenone unsaturation</t>
+    <t xml:space="preserve">published Uk37 temperature</t>
   </si>
   <si>
     <t xml:space="preserve">range of 0.14 to 0.39 micro molar with central value of 0.20; Conkright et al., WOA2001</t>
@@ -1595,177 +1595,267 @@
     <t xml:space="preserve">phytoplankton_Pagani_2010_69</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_52</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_15</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_70</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_53</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_16</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_71</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_54</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_17</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_72</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_55</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_18</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_73</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_56</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_19</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_74</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_57</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_20</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_75</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_58</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_21</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_76</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_59</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_22</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_77</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_60</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_23</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_78</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_61</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_24</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_79</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_62</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_25</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_80</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_63</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_26</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_81</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_64</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_27</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_82</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_65</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_28</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_83</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_66</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_29</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_84</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_67</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_30</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_85</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_68</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_31</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_86</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_69</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_32</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_87</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_70</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_33</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_88</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_71</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_34</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_90</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_72</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_35</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_91</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_73</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_36</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_93</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_74</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_37</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_94</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_75</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_38</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_95</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_76</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_39</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_96</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_77</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_40</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_97</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_78</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_41</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_98</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_79</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_42</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_99</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_80</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_43</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_81</t>
+  </si>
+  <si>
     <t xml:space="preserve">original carbonate d13C data</t>
   </si>
   <si>
@@ -1775,48 +1865,75 @@
     <t xml:space="preserve">phytoplankton_Pagani_2010_100</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_82</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_45</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_101</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_83</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_46</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_102</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_84</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_47</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_103</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_85</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_48</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_104</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_86</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_49</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_105</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_87</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_50</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Pagani_2010_106</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_88</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_51</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_89</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_52</t>
   </si>
   <si>
+    <t xml:space="preserve">phytoplankton_Rae_2021_90</t>
+  </si>
+  <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_53</t>
   </si>
   <si>
@@ -1826,7 +1943,7 @@
     <t xml:space="preserve">phytoplankton_Zhang_2013_55</t>
   </si>
   <si>
-    <t xml:space="preserve">TEX86</t>
+    <t xml:space="preserve">average of published Uk37 and TEX86 temperatures</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Zhang_2013_56</t>
@@ -1848,6 +1965,213 @@
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_pagani_2011_58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Pagani_2011_74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_zhang_2020_49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Zhang_2013_89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_pagani_2011_88</t>
   </si>
 </sst>
 </file>
@@ -1855,7 +2179,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1921,12 +2245,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -2040,7 +2358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2139,7 +2457,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2865,7 +3182,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2883,8 +3200,8 @@
       <c r="H5" t="n">
         <v>0.02</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2902,7 +3219,7 @@
         <v>-23.871</v>
       </c>
       <c r="O5" t="n">
-        <v>0.073999999999998</v>
+        <v>0.0523259018078031</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2913,8 +3230,8 @@
       <c r="R5" s="11" t="n">
         <v>27.3609307904087</v>
       </c>
-      <c r="S5" t="e">
-        <v>#N/A</v>
+      <c r="S5" t="n">
+        <v>3</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2932,28 +3249,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA5" t="s">
         <v>278</v>
       </c>
-      <c r="AB5" t="e">
-        <v>#N/A</v>
+      <c r="AB5" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF5" t="e">
-        <v>#N/A</v>
+      <c r="AD5" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG5" t="e">
         <v>#N/A</v>
@@ -2975,7 +3292,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2993,8 +3310,8 @@
       <c r="H6" t="n">
         <v>0.028</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.004</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -3012,7 +3329,7 @@
         <v>-23.543</v>
       </c>
       <c r="O6" t="n">
-        <v>0.118000000000002</v>
+        <v>0.0834386001800141</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -3023,8 +3340,8 @@
       <c r="R6" s="11" t="n">
         <v>27.0868678285204</v>
       </c>
-      <c r="S6" t="e">
-        <v>#N/A</v>
+      <c r="S6" t="n">
+        <v>3</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -3042,28 +3359,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA6" t="s">
         <v>278</v>
       </c>
-      <c r="AB6" t="e">
-        <v>#N/A</v>
+      <c r="AB6" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" t="e">
-        <v>#N/A</v>
+      <c r="AD6" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG6" t="e">
         <v>#N/A</v>
@@ -3085,7 +3402,7 @@
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -3103,8 +3420,8 @@
       <c r="H7" t="n">
         <v>0.0335</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.004</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -3122,7 +3439,7 @@
         <v>-24.05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.414000000000002</v>
+        <v>0.292742207411232</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -3133,8 +3450,8 @@
       <c r="R7" s="11" t="n">
         <v>27.2979276226908</v>
       </c>
-      <c r="S7" t="e">
-        <v>#N/A</v>
+      <c r="S7" t="n">
+        <v>3</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -3152,28 +3469,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA7" t="s">
         <v>278</v>
       </c>
-      <c r="AB7" t="e">
-        <v>#N/A</v>
+      <c r="AB7" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF7" t="e">
-        <v>#N/A</v>
+      <c r="AD7" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG7" t="e">
         <v>#N/A</v>
@@ -3195,7 +3512,7 @@
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -3213,8 +3530,8 @@
       <c r="H8" t="n">
         <v>0.0412</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.004</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -3232,7 +3549,7 @@
         <v>-23.8055</v>
       </c>
       <c r="O8" t="n">
-        <v>0.149999999999999</v>
+        <v>0.106066017177981</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -3243,8 +3560,8 @@
       <c r="R8" s="11" t="n">
         <v>26.5197796133824</v>
       </c>
-      <c r="S8" t="e">
-        <v>#N/A</v>
+      <c r="S8" t="n">
+        <v>3</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -3262,28 +3579,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA8" t="s">
         <v>278</v>
       </c>
-      <c r="AB8" t="e">
-        <v>#N/A</v>
+      <c r="AB8" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF8" t="e">
-        <v>#N/A</v>
+      <c r="AD8" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG8" t="e">
         <v>#N/A</v>
@@ -3305,7 +3622,7 @@
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3323,8 +3640,8 @@
       <c r="H9" t="n">
         <v>0.0583</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3342,7 +3659,7 @@
         <v>-23.969</v>
       </c>
       <c r="O9" t="n">
-        <v>0.488</v>
+        <v>0.345068109219035</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3353,8 +3670,8 @@
       <c r="R9" s="11" t="n">
         <v>27.0108617900447</v>
       </c>
-      <c r="S9" t="e">
-        <v>#N/A</v>
+      <c r="S9" t="n">
+        <v>3</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3372,28 +3689,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA9" t="s">
         <v>278</v>
       </c>
-      <c r="AB9" t="e">
-        <v>#N/A</v>
+      <c r="AB9" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" t="e">
-        <v>#N/A</v>
+      <c r="AD9" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG9" t="e">
         <v>#N/A</v>
@@ -3415,7 +3732,7 @@
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3433,8 +3750,8 @@
       <c r="H10" t="n">
         <v>0.0736</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.004</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3452,7 +3769,7 @@
         <v>-24.34</v>
       </c>
       <c r="O10" t="n">
-        <v>0.224000000000004</v>
+        <v>0.158391918985789</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3463,8 +3780,8 @@
       <c r="R10" s="11" t="n">
         <v>27.5714296899851</v>
       </c>
-      <c r="S10" t="e">
-        <v>#N/A</v>
+      <c r="S10" t="n">
+        <v>3</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3482,28 +3799,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA10" t="s">
         <v>278</v>
       </c>
-      <c r="AB10" t="e">
-        <v>#N/A</v>
+      <c r="AB10" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF10" t="e">
-        <v>#N/A</v>
+      <c r="AD10" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG10" t="e">
         <v>#N/A</v>
@@ -3525,7 +3842,7 @@
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3543,8 +3860,8 @@
       <c r="H11" t="n">
         <v>0.0893</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.004</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3562,7 +3879,7 @@
         <v>-24.2365</v>
       </c>
       <c r="O11" t="n">
-        <v>0.405999999999998</v>
+        <v>0.287085353161737</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3573,8 +3890,8 @@
       <c r="R11" s="11" t="n">
         <v>27.6391486612016</v>
       </c>
-      <c r="S11" t="e">
-        <v>#N/A</v>
+      <c r="S11" t="n">
+        <v>3</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3592,28 +3909,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA11" t="s">
         <v>278</v>
       </c>
-      <c r="AB11" t="e">
-        <v>#N/A</v>
+      <c r="AB11" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF11" t="e">
-        <v>#N/A</v>
+      <c r="AD11" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG11" t="e">
         <v>#N/A</v>
@@ -3635,7 +3952,7 @@
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3653,8 +3970,8 @@
       <c r="H12" t="n">
         <v>0.1054</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.004</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3672,7 +3989,7 @@
         <v>-23.994</v>
       </c>
       <c r="O12" t="n">
-        <v>0.100000000000001</v>
+        <v>0.0707106781186558</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3683,8 +4000,8 @@
       <c r="R12" s="11" t="n">
         <v>27.7245663249025</v>
       </c>
-      <c r="S12" t="e">
-        <v>#N/A</v>
+      <c r="S12" t="n">
+        <v>3</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3702,28 +4019,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA12" t="s">
         <v>278</v>
       </c>
-      <c r="AB12" t="e">
-        <v>#N/A</v>
+      <c r="AB12" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" t="e">
-        <v>#N/A</v>
+      <c r="AD12" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG12" t="e">
         <v>#N/A</v>
@@ -3745,7 +4062,7 @@
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3763,8 +4080,8 @@
       <c r="H13" t="n">
         <v>0.1132</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.004</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3782,7 +4099,7 @@
         <v>-24.3845</v>
       </c>
       <c r="O13" t="n">
-        <v>0.167999999999999</v>
+        <v>0.118793939239339</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3793,8 +4110,8 @@
       <c r="R13" s="11" t="n">
         <v>27.7676957516199</v>
       </c>
-      <c r="S13" t="e">
-        <v>#N/A</v>
+      <c r="S13" t="n">
+        <v>3</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3812,28 +4129,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA13" t="s">
         <v>278</v>
       </c>
-      <c r="AB13" t="e">
-        <v>#N/A</v>
+      <c r="AB13" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF13" t="e">
-        <v>#N/A</v>
+      <c r="AD13" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG13" t="e">
         <v>#N/A</v>
@@ -3855,7 +4172,7 @@
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3873,8 +4190,8 @@
       <c r="H14" t="n">
         <v>0.1336</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.004</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3892,7 +4209,7 @@
         <v>-24.6465</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0660000000000026</v>
+        <v>0.0466690475583139</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3903,8 +4220,8 @@
       <c r="R14" s="11" t="n">
         <v>27.8451059508084</v>
       </c>
-      <c r="S14" t="e">
-        <v>#N/A</v>
+      <c r="S14" t="n">
+        <v>3</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3922,28 +4239,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA14" t="s">
         <v>278</v>
       </c>
-      <c r="AB14" t="e">
-        <v>#N/A</v>
+      <c r="AB14" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" t="e">
-        <v>#N/A</v>
+      <c r="AD14" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG14" t="e">
         <v>#N/A</v>
@@ -3965,7 +4282,7 @@
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3983,8 +4300,8 @@
       <c r="H15" t="n">
         <v>0.1465</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.004</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -4002,7 +4319,7 @@
         <v>-24.3855</v>
       </c>
       <c r="O15" t="n">
-        <v>0.324000000000006</v>
+        <v>0.229102597104445</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -4013,8 +4330,8 @@
       <c r="R15" s="11" t="n">
         <v>27.5888920032959</v>
       </c>
-      <c r="S15" t="e">
-        <v>#N/A</v>
+      <c r="S15" t="n">
+        <v>3</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -4032,28 +4349,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA15" t="s">
         <v>278</v>
       </c>
-      <c r="AB15" t="e">
-        <v>#N/A</v>
+      <c r="AB15" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" t="e">
-        <v>#N/A</v>
+      <c r="AD15" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG15" t="e">
         <v>#N/A</v>
@@ -4075,7 +4392,7 @@
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -4093,8 +4410,8 @@
       <c r="H16" t="n">
         <v>0.1562</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.004</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -4112,7 +4429,7 @@
         <v>-24.1665</v>
       </c>
       <c r="O16" t="n">
-        <v>0.298000000000002</v>
+        <v>0.210717820793592</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -4123,8 +4440,8 @@
       <c r="R16" s="11" t="n">
         <v>27.2234360490266</v>
       </c>
-      <c r="S16" t="e">
-        <v>#N/A</v>
+      <c r="S16" t="n">
+        <v>3</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -4142,28 +4459,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA16" t="s">
         <v>278</v>
       </c>
-      <c r="AB16" t="e">
-        <v>#N/A</v>
+      <c r="AB16" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF16" t="e">
-        <v>#N/A</v>
+      <c r="AD16" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG16" t="e">
         <v>#N/A</v>
@@ -4185,7 +4502,7 @@
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -4203,8 +4520,8 @@
       <c r="H17" t="n">
         <v>0.1666</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.004</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -4222,7 +4539,7 @@
         <v>-24.5575</v>
       </c>
       <c r="O17" t="n">
-        <v>0.395999999999994</v>
+        <v>0.280014285349868</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -4233,8 +4550,8 @@
       <c r="R17" s="11" t="n">
         <v>27.084384263311</v>
       </c>
-      <c r="S17" t="e">
-        <v>#N/A</v>
+      <c r="S17" t="n">
+        <v>3</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -4252,28 +4569,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA17" t="s">
         <v>278</v>
       </c>
-      <c r="AB17" t="e">
-        <v>#N/A</v>
+      <c r="AB17" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF17" t="e">
-        <v>#N/A</v>
+      <c r="AD17" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG17" t="e">
         <v>#N/A</v>
@@ -4295,7 +4612,7 @@
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4313,8 +4630,8 @@
       <c r="H18" t="n">
         <v>0.31</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.004</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4332,7 +4649,7 @@
         <v>-23.767</v>
       </c>
       <c r="O18" t="n">
-        <v>0.327999999999996</v>
+        <v>0.231931024229185</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4343,8 +4660,8 @@
       <c r="R18" s="11" t="n">
         <v>27.41856917476</v>
       </c>
-      <c r="S18" t="e">
-        <v>#N/A</v>
+      <c r="S18" t="n">
+        <v>3</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -4362,28 +4679,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA18" t="s">
         <v>278</v>
       </c>
-      <c r="AB18" t="e">
-        <v>#N/A</v>
+      <c r="AB18" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" t="e">
-        <v>#N/A</v>
+      <c r="AD18" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG18" t="e">
         <v>#N/A</v>
@@ -4391,8 +4708,8 @@
       <c r="AH18" t="s">
         <v>316</v>
       </c>
-      <c r="AI18" t="e">
-        <v>#N/A</v>
+      <c r="AI18" t="s">
+        <v>317</v>
       </c>
       <c r="AJ18" t="s">
         <v>287</v>
@@ -4400,12 +4717,12 @@
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4423,8 +4740,8 @@
       <c r="H19" t="n">
         <v>0.431</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.004</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4442,7 +4759,7 @@
         <v>-22.9245</v>
       </c>
       <c r="O19" t="n">
-        <v>0.735999999999998</v>
+        <v>0.520430590953297</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4453,8 +4770,8 @@
       <c r="R19" s="11" t="n">
         <v>26.8564031451013</v>
       </c>
-      <c r="S19" t="e">
-        <v>#N/A</v>
+      <c r="S19" t="n">
+        <v>3</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -4472,37 +4789,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA19" t="s">
         <v>278</v>
       </c>
-      <c r="AB19" t="e">
-        <v>#N/A</v>
+      <c r="AB19" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF19" t="e">
-        <v>#N/A</v>
+      <c r="AD19" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG19" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH19" t="s">
-        <v>318</v>
-      </c>
-      <c r="AI19" t="e">
-        <v>#N/A</v>
+        <v>319</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>320</v>
       </c>
       <c r="AJ19" t="s">
         <v>287</v>
@@ -4510,12 +4827,12 @@
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4533,8 +4850,8 @@
       <c r="H20" t="n">
         <v>0.5753</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.004</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4552,7 +4869,7 @@
         <v>-22.9975</v>
       </c>
       <c r="O20" t="n">
-        <v>0.265999999999998</v>
+        <v>0.18809040379562</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4563,8 +4880,8 @@
       <c r="R20" s="11" t="n">
         <v>27.7522297695142</v>
       </c>
-      <c r="S20" t="e">
-        <v>#N/A</v>
+      <c r="S20" t="n">
+        <v>3</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -4582,37 +4899,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA20" t="s">
         <v>278</v>
       </c>
-      <c r="AB20" t="e">
-        <v>#N/A</v>
+      <c r="AB20" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF20" t="e">
-        <v>#N/A</v>
+      <c r="AD20" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG20" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH20" t="s">
-        <v>320</v>
-      </c>
-      <c r="AI20" t="e">
-        <v>#N/A</v>
+        <v>322</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>323</v>
       </c>
       <c r="AJ20" t="s">
         <v>287</v>
@@ -4620,12 +4937,12 @@
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4643,8 +4960,8 @@
       <c r="H21" t="n">
         <v>0.9287</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.004</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4662,7 +4979,7 @@
         <v>-23.5185</v>
       </c>
       <c r="O21" t="n">
-        <v>0.880000000000002</v>
+        <v>0.622253967444164</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4673,8 +4990,8 @@
       <c r="R21" s="11" t="n">
         <v>26.8474188031653</v>
       </c>
-      <c r="S21" t="e">
-        <v>#N/A</v>
+      <c r="S21" t="n">
+        <v>3</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -4692,37 +5009,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA21" t="s">
         <v>278</v>
       </c>
-      <c r="AB21" t="e">
-        <v>#N/A</v>
+      <c r="AB21" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" t="e">
-        <v>#N/A</v>
+      <c r="AD21" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG21" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH21" t="s">
-        <v>322</v>
-      </c>
-      <c r="AI21" t="e">
-        <v>#N/A</v>
+        <v>325</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>326</v>
       </c>
       <c r="AJ21" t="s">
         <v>287</v>
@@ -4730,12 +5047,12 @@
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4753,8 +5070,8 @@
       <c r="H22" t="n">
         <v>1.046</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.006</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4772,7 +5089,7 @@
         <v>-23.7335</v>
       </c>
       <c r="O22" t="n">
-        <v>0.531999999999996</v>
+        <v>0.376180807591241</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4783,8 +5100,8 @@
       <c r="R22" s="11" t="n">
         <v>27.2986076191685</v>
       </c>
-      <c r="S22" t="e">
-        <v>#N/A</v>
+      <c r="S22" t="n">
+        <v>3</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -4802,37 +5119,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA22" t="s">
         <v>278</v>
       </c>
-      <c r="AB22" t="e">
-        <v>#N/A</v>
+      <c r="AB22" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#N/A</v>
+      <c r="AD22" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG22" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH22" t="s">
-        <v>324</v>
-      </c>
-      <c r="AI22" t="e">
-        <v>#N/A</v>
+        <v>328</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>329</v>
       </c>
       <c r="AJ22" t="s">
         <v>287</v>
@@ -4840,12 +5157,12 @@
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4863,8 +5180,8 @@
       <c r="H23" t="n">
         <v>1.191</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.006</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4882,7 +5199,7 @@
         <v>-23.9325</v>
       </c>
       <c r="O23" t="n">
-        <v>0.332000000000008</v>
+        <v>0.234759451353939</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4893,8 +5210,8 @@
       <c r="R23" s="11" t="n">
         <v>27.5222351262273</v>
       </c>
-      <c r="S23" t="e">
-        <v>#N/A</v>
+      <c r="S23" t="n">
+        <v>3</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -4912,37 +5229,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA23" t="s">
         <v>278</v>
       </c>
-      <c r="AB23" t="e">
-        <v>#N/A</v>
+      <c r="AB23" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF23" t="e">
-        <v>#N/A</v>
+      <c r="AD23" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG23" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH23" t="s">
-        <v>326</v>
-      </c>
-      <c r="AI23" t="e">
-        <v>#N/A</v>
+        <v>331</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>332</v>
       </c>
       <c r="AJ23" t="s">
         <v>287</v>
@@ -4950,12 +5267,12 @@
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4973,8 +5290,8 @@
       <c r="H24" t="n">
         <v>1.206</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.006</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4992,7 +5309,7 @@
         <v>-23.446</v>
       </c>
       <c r="O24" t="n">
-        <v>0.102000000000004</v>
+        <v>0.0721248916810306</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -5003,8 +5320,8 @@
       <c r="R24" s="11" t="n">
         <v>27.742472598525</v>
       </c>
-      <c r="S24" t="e">
-        <v>#N/A</v>
+      <c r="S24" t="n">
+        <v>3</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -5022,37 +5339,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA24" t="s">
         <v>278</v>
       </c>
-      <c r="AB24" t="e">
-        <v>#N/A</v>
+      <c r="AB24" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" t="e">
-        <v>#N/A</v>
+      <c r="AD24" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG24" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH24" t="s">
-        <v>328</v>
-      </c>
-      <c r="AI24" t="e">
-        <v>#N/A</v>
+        <v>334</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>335</v>
       </c>
       <c r="AJ24" t="s">
         <v>287</v>
@@ -5060,12 +5377,12 @@
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -5083,8 +5400,8 @@
       <c r="H25" t="n">
         <v>1.2188</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.006</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -5102,7 +5419,7 @@
         <v>-23.6415</v>
       </c>
       <c r="O25" t="n">
-        <v>0.326</v>
+        <v>0.230516810666815</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -5113,8 +5430,8 @@
       <c r="R25" s="11" t="n">
         <v>27.7009080062643</v>
       </c>
-      <c r="S25" t="e">
-        <v>#N/A</v>
+      <c r="S25" t="n">
+        <v>3</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -5132,37 +5449,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA25" t="s">
         <v>278</v>
       </c>
-      <c r="AB25" t="e">
-        <v>#N/A</v>
+      <c r="AB25" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#N/A</v>
+      <c r="AD25" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG25" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH25" t="s">
-        <v>330</v>
-      </c>
-      <c r="AI25" t="e">
-        <v>#N/A</v>
+        <v>337</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>338</v>
       </c>
       <c r="AJ25" t="s">
         <v>287</v>
@@ -5170,12 +5487,12 @@
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -5193,8 +5510,8 @@
       <c r="H26" t="n">
         <v>1.2322</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.006</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -5212,7 +5529,7 @@
         <v>-23.718</v>
       </c>
       <c r="O26" t="n">
-        <v>0.268</v>
+        <v>0.189504617357995</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -5223,8 +5540,8 @@
       <c r="R26" s="11" t="n">
         <v>27.8823591559305</v>
       </c>
-      <c r="S26" t="e">
-        <v>#N/A</v>
+      <c r="S26" t="n">
+        <v>3</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -5242,37 +5559,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA26" t="s">
         <v>278</v>
       </c>
-      <c r="AB26" t="e">
-        <v>#N/A</v>
+      <c r="AB26" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF26" t="e">
-        <v>#N/A</v>
+      <c r="AD26" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG26" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH26" t="s">
-        <v>332</v>
-      </c>
-      <c r="AI26" t="e">
-        <v>#N/A</v>
+        <v>340</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>341</v>
       </c>
       <c r="AJ26" t="s">
         <v>287</v>
@@ -5280,12 +5597,12 @@
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5303,8 +5620,8 @@
       <c r="H27" t="n">
         <v>1.25</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.006</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5321,8 +5638,8 @@
       <c r="N27" t="n">
         <v>-23.072</v>
       </c>
-      <c r="O27" t="e">
-        <v>#N/A</v>
+      <c r="O27" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -5333,8 +5650,8 @@
       <c r="R27" s="11" t="n">
         <v>26.8897521988575</v>
       </c>
-      <c r="S27" t="e">
-        <v>#N/A</v>
+      <c r="S27" t="n">
+        <v>3</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
@@ -5352,37 +5669,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA27" t="s">
         <v>278</v>
       </c>
-      <c r="AB27" t="e">
-        <v>#N/A</v>
+      <c r="AB27" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" t="e">
-        <v>#N/A</v>
+      <c r="AD27" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG27" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH27" t="s">
-        <v>334</v>
-      </c>
-      <c r="AI27" t="e">
-        <v>#N/A</v>
+        <v>343</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>344</v>
       </c>
       <c r="AJ27" t="s">
         <v>287</v>
@@ -5390,12 +5707,12 @@
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5413,8 +5730,8 @@
       <c r="H28" t="n">
         <v>1.272</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.006</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5432,7 +5749,7 @@
         <v>-22.991</v>
       </c>
       <c r="O28" t="n">
-        <v>0.834000000000004</v>
+        <v>0.589727055509583</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5443,8 +5760,8 @@
       <c r="R28" s="11" t="n">
         <v>27.588231840995</v>
       </c>
-      <c r="S28" t="e">
-        <v>#N/A</v>
+      <c r="S28" t="n">
+        <v>3</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
@@ -5462,37 +5779,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA28" t="s">
         <v>278</v>
       </c>
-      <c r="AB28" t="e">
-        <v>#N/A</v>
+      <c r="AB28" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF28" t="e">
-        <v>#N/A</v>
+      <c r="AD28" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG28" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH28" t="s">
-        <v>336</v>
-      </c>
-      <c r="AI28" t="e">
-        <v>#N/A</v>
+        <v>346</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>347</v>
       </c>
       <c r="AJ28" t="s">
         <v>287</v>
@@ -5500,12 +5817,12 @@
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5523,8 +5840,8 @@
       <c r="H29" t="n">
         <v>1.2846</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.006</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5542,7 +5859,7 @@
         <v>-23.3085</v>
       </c>
       <c r="O29" t="n">
-        <v>0.734000000000002</v>
+        <v>0.519016377390927</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5553,8 +5870,8 @@
       <c r="R29" s="11" t="n">
         <v>27.3814044429103</v>
       </c>
-      <c r="S29" t="e">
-        <v>#N/A</v>
+      <c r="S29" t="n">
+        <v>3</v>
       </c>
       <c r="T29" t="e">
         <v>#N/A</v>
@@ -5572,37 +5889,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA29" t="s">
         <v>278</v>
       </c>
-      <c r="AB29" t="e">
-        <v>#N/A</v>
+      <c r="AB29" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF29" t="e">
-        <v>#N/A</v>
+      <c r="AD29" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG29" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH29" t="s">
-        <v>338</v>
-      </c>
-      <c r="AI29" t="e">
-        <v>#N/A</v>
+        <v>349</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>350</v>
       </c>
       <c r="AJ29" t="s">
         <v>287</v>
@@ -5610,12 +5927,12 @@
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5633,8 +5950,8 @@
       <c r="H30" t="n">
         <v>1.3512</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.006</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5652,7 +5969,7 @@
         <v>-23.4775</v>
       </c>
       <c r="O30" t="n">
-        <v>0.506</v>
+        <v>0.357796031280393</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5663,8 +5980,8 @@
       <c r="R30" s="11" t="n">
         <v>27.6665316202811</v>
       </c>
-      <c r="S30" t="e">
-        <v>#N/A</v>
+      <c r="S30" t="n">
+        <v>3</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -5682,37 +5999,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA30" t="s">
         <v>278</v>
       </c>
-      <c r="AB30" t="e">
-        <v>#N/A</v>
+      <c r="AB30" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" t="e">
-        <v>#N/A</v>
+      <c r="AD30" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG30" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH30" t="s">
-        <v>340</v>
-      </c>
-      <c r="AI30" t="e">
-        <v>#N/A</v>
+        <v>352</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>353</v>
       </c>
       <c r="AJ30" t="s">
         <v>287</v>
@@ -5720,12 +6037,12 @@
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5743,8 +6060,8 @@
       <c r="H31" t="n">
         <v>1.6407</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.006</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5762,7 +6079,7 @@
         <v>-23.8455</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0459999999999994</v>
+        <v>0.0325269119345807</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5773,8 +6090,8 @@
       <c r="R31" s="11" t="n">
         <v>26.3807039618973</v>
       </c>
-      <c r="S31" t="e">
-        <v>#N/A</v>
+      <c r="S31" t="n">
+        <v>3</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -5792,37 +6109,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA31" t="s">
         <v>278</v>
       </c>
-      <c r="AB31" t="e">
-        <v>#N/A</v>
+      <c r="AB31" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#N/A</v>
+      <c r="AD31" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG31" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH31" t="s">
-        <v>342</v>
-      </c>
-      <c r="AI31" t="e">
-        <v>#N/A</v>
+        <v>355</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>356</v>
       </c>
       <c r="AJ31" t="s">
         <v>287</v>
@@ -5830,12 +6147,12 @@
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5853,8 +6170,8 @@
       <c r="H32" t="n">
         <v>1.7295</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.006</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5872,7 +6189,7 @@
         <v>-23.7515</v>
       </c>
       <c r="O32" t="n">
-        <v>0.369999999999998</v>
+        <v>0.261629509039021</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -5883,8 +6200,8 @@
       <c r="R32" s="11" t="n">
         <v>27.7356215670018</v>
       </c>
-      <c r="S32" t="e">
-        <v>#N/A</v>
+      <c r="S32" t="n">
+        <v>3</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -5902,37 +6219,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA32" t="s">
         <v>278</v>
       </c>
-      <c r="AB32" t="e">
-        <v>#N/A</v>
+      <c r="AB32" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF32" t="e">
-        <v>#N/A</v>
+      <c r="AD32" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG32" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH32" t="s">
-        <v>344</v>
-      </c>
-      <c r="AI32" t="e">
-        <v>#N/A</v>
+        <v>358</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>359</v>
       </c>
       <c r="AJ32" t="s">
         <v>287</v>
@@ -5940,12 +6257,12 @@
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B33" t="s">
         <v>271</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" t="s">
         <v>272</v>
       </c>
       <c r="D33" t="s">
@@ -5963,8 +6280,8 @@
       <c r="H33" t="n">
         <v>1.965</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.006</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -5982,7 +6299,7 @@
         <v>-23.699</v>
       </c>
       <c r="O33" t="n">
-        <v>0.210000000000008</v>
+        <v>0.148492424049181</v>
       </c>
       <c r="P33" t="e">
         <v>#N/A</v>
@@ -5993,8 +6310,8 @@
       <c r="R33" s="11" t="n">
         <v>27.839598329138</v>
       </c>
-      <c r="S33" t="e">
-        <v>#N/A</v>
+      <c r="S33" t="n">
+        <v>3</v>
       </c>
       <c r="T33" t="e">
         <v>#N/A</v>
@@ -6012,37 +6329,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA33" t="s">
         <v>278</v>
       </c>
-      <c r="AB33" t="e">
-        <v>#N/A</v>
+      <c r="AB33" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF33" t="e">
-        <v>#N/A</v>
+      <c r="AD33" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG33" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH33" t="s">
-        <v>346</v>
-      </c>
-      <c r="AI33" t="e">
-        <v>#N/A</v>
+        <v>361</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>362</v>
       </c>
       <c r="AJ33" t="s">
         <v>287</v>
@@ -6050,12 +6367,12 @@
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="B34" t="s">
         <v>271</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" t="s">
         <v>272</v>
       </c>
       <c r="D34" t="s">
@@ -6073,8 +6390,8 @@
       <c r="H34" t="n">
         <v>2.0926</v>
       </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+      <c r="I34" t="n">
+        <v>0.006</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -6092,7 +6409,7 @@
         <v>-24.1195</v>
       </c>
       <c r="O34" t="n">
-        <v>0.363999999999998</v>
+        <v>0.257386868351901</v>
       </c>
       <c r="P34" t="e">
         <v>#N/A</v>
@@ -6103,8 +6420,8 @@
       <c r="R34" s="11" t="n">
         <v>27.836764842377</v>
       </c>
-      <c r="S34" t="e">
-        <v>#N/A</v>
+      <c r="S34" t="n">
+        <v>3</v>
       </c>
       <c r="T34" t="e">
         <v>#N/A</v>
@@ -6122,37 +6439,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA34" t="s">
         <v>278</v>
       </c>
-      <c r="AB34" t="e">
-        <v>#N/A</v>
+      <c r="AB34" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF34" t="e">
-        <v>#N/A</v>
+      <c r="AD34" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG34" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH34" t="s">
-        <v>348</v>
-      </c>
-      <c r="AI34" t="e">
-        <v>#N/A</v>
+        <v>364</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>365</v>
       </c>
       <c r="AJ34" t="s">
         <v>287</v>
@@ -6160,12 +6477,12 @@
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="B35" t="s">
         <v>271</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" t="s">
         <v>272</v>
       </c>
       <c r="D35" t="s">
@@ -6183,8 +6500,8 @@
       <c r="H35" t="n">
         <v>2.1915</v>
       </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+      <c r="I35" t="n">
+        <v>0.006</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -6201,8 +6518,8 @@
       <c r="N35" t="n">
         <v>-23.736</v>
       </c>
-      <c r="O35" t="e">
-        <v>#N/A</v>
+      <c r="O35" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P35" t="e">
         <v>#N/A</v>
@@ -6213,8 +6530,8 @@
       <c r="R35" s="11" t="n">
         <v>28.2647058823529</v>
       </c>
-      <c r="S35" t="e">
-        <v>#N/A</v>
+      <c r="S35" t="n">
+        <v>3</v>
       </c>
       <c r="T35" t="e">
         <v>#N/A</v>
@@ -6232,37 +6549,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA35" t="s">
         <v>278</v>
       </c>
-      <c r="AB35" t="e">
-        <v>#N/A</v>
+      <c r="AB35" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF35" t="e">
-        <v>#N/A</v>
+      <c r="AD35" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG35" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH35" t="s">
-        <v>350</v>
-      </c>
-      <c r="AI35" t="e">
-        <v>#N/A</v>
+        <v>367</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>368</v>
       </c>
       <c r="AJ35" t="s">
         <v>287</v>
@@ -6270,12 +6587,12 @@
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B36" t="s">
         <v>271</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" t="s">
         <v>272</v>
       </c>
       <c r="D36" t="s">
@@ -6293,8 +6610,8 @@
       <c r="H36" t="n">
         <v>2.2968</v>
       </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+      <c r="I36" t="n">
+        <v>0.006</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -6312,7 +6629,7 @@
         <v>-24.363</v>
       </c>
       <c r="O36" t="n">
-        <v>0.152000000000001</v>
+        <v>0.107480230740356</v>
       </c>
       <c r="P36" t="e">
         <v>#N/A</v>
@@ -6323,8 +6640,8 @@
       <c r="R36" s="11" t="n">
         <v>27.8176403379106</v>
       </c>
-      <c r="S36" t="e">
-        <v>#N/A</v>
+      <c r="S36" t="n">
+        <v>3</v>
       </c>
       <c r="T36" t="e">
         <v>#N/A</v>
@@ -6342,37 +6659,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA36" t="s">
         <v>278</v>
       </c>
-      <c r="AB36" t="e">
-        <v>#N/A</v>
+      <c r="AB36" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF36" t="e">
-        <v>#N/A</v>
+      <c r="AD36" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG36" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH36" t="s">
-        <v>352</v>
-      </c>
-      <c r="AI36" t="e">
-        <v>#N/A</v>
+        <v>370</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>371</v>
       </c>
       <c r="AJ36" t="s">
         <v>287</v>
@@ -6380,12 +6697,12 @@
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s">
         <v>271</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" t="s">
         <v>272</v>
       </c>
       <c r="D37" t="s">
@@ -6403,8 +6720,8 @@
       <c r="H37" t="n">
         <v>2.402</v>
       </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+      <c r="I37" t="n">
+        <v>0.006</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -6422,7 +6739,7 @@
         <v>-24.401</v>
       </c>
       <c r="O37" t="n">
-        <v>0.033999999999999</v>
+        <v>0.0240416305603419</v>
       </c>
       <c r="P37" t="e">
         <v>#N/A</v>
@@ -6433,8 +6750,8 @@
       <c r="R37" s="11" t="n">
         <v>27.9631956499446</v>
       </c>
-      <c r="S37" t="e">
-        <v>#N/A</v>
+      <c r="S37" t="n">
+        <v>3</v>
       </c>
       <c r="T37" t="e">
         <v>#N/A</v>
@@ -6452,37 +6769,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA37" t="s">
         <v>278</v>
       </c>
-      <c r="AB37" t="e">
-        <v>#N/A</v>
+      <c r="AB37" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF37" t="e">
-        <v>#N/A</v>
+      <c r="AD37" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG37" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH37" t="s">
-        <v>354</v>
-      </c>
-      <c r="AI37" t="e">
-        <v>#N/A</v>
+        <v>373</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>374</v>
       </c>
       <c r="AJ37" t="s">
         <v>287</v>
@@ -6490,12 +6807,12 @@
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="B38" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="C38" t="s">
         <v>272</v>
       </c>
       <c r="D38" t="s">
@@ -6513,8 +6830,8 @@
       <c r="H38" t="n">
         <v>2.587</v>
       </c>
-      <c r="I38" t="e">
-        <v>#N/A</v>
+      <c r="I38" t="n">
+        <v>0.006</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -6532,7 +6849,7 @@
         <v>-24.413</v>
       </c>
       <c r="O38" t="n">
-        <v>0.212000000000004</v>
+        <v>0.14990663761155</v>
       </c>
       <c r="P38" t="e">
         <v>#N/A</v>
@@ -6543,8 +6860,8 @@
       <c r="R38" s="11" t="n">
         <v>27.8842636953312</v>
       </c>
-      <c r="S38" t="e">
-        <v>#N/A</v>
+      <c r="S38" t="n">
+        <v>3</v>
       </c>
       <c r="T38" t="e">
         <v>#N/A</v>
@@ -6562,37 +6879,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA38" t="s">
         <v>278</v>
       </c>
-      <c r="AB38" t="e">
-        <v>#N/A</v>
+      <c r="AB38" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF38" t="e">
-        <v>#N/A</v>
+      <c r="AD38" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG38" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH38" t="s">
-        <v>356</v>
-      </c>
-      <c r="AI38" t="e">
-        <v>#N/A</v>
+        <v>376</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>377</v>
       </c>
       <c r="AJ38" t="s">
         <v>287</v>
@@ -6600,12 +6917,12 @@
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="B39" t="s">
         <v>271</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" t="s">
         <v>272</v>
       </c>
       <c r="D39" t="s">
@@ -6623,8 +6940,8 @@
       <c r="H39" t="n">
         <v>2.6043</v>
       </c>
-      <c r="I39" t="e">
-        <v>#N/A</v>
+      <c r="I39" t="n">
+        <v>0.006</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -6642,7 +6959,7 @@
         <v>-23.5705</v>
       </c>
       <c r="O39" t="n">
-        <v>0.666000000000004</v>
+        <v>0.470933116270243</v>
       </c>
       <c r="P39" t="e">
         <v>#N/A</v>
@@ -6653,8 +6970,8 @@
       <c r="R39" s="11" t="n">
         <v>27.5466047802869</v>
       </c>
-      <c r="S39" t="e">
-        <v>#N/A</v>
+      <c r="S39" t="n">
+        <v>3</v>
       </c>
       <c r="T39" t="e">
         <v>#N/A</v>
@@ -6672,37 +6989,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA39" t="s">
         <v>278</v>
       </c>
-      <c r="AB39" t="e">
-        <v>#N/A</v>
+      <c r="AB39" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF39" t="e">
-        <v>#N/A</v>
+      <c r="AD39" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG39" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH39" t="s">
-        <v>358</v>
-      </c>
-      <c r="AI39" t="e">
-        <v>#N/A</v>
+        <v>379</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>380</v>
       </c>
       <c r="AJ39" t="s">
         <v>287</v>
@@ -6710,12 +7027,12 @@
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="B40" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C40" t="s">
         <v>272</v>
       </c>
       <c r="D40" t="s">
@@ -6733,8 +7050,8 @@
       <c r="H40" t="n">
         <v>2.718</v>
       </c>
-      <c r="I40" t="e">
-        <v>#N/A</v>
+      <c r="I40" t="n">
+        <v>0.006</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -6752,7 +7069,7 @@
         <v>-24.0765</v>
       </c>
       <c r="O40" t="n">
-        <v>0.46</v>
+        <v>0.325269119345812</v>
       </c>
       <c r="P40" t="e">
         <v>#N/A</v>
@@ -6763,8 +7080,8 @@
       <c r="R40" s="11" t="n">
         <v>27.8590452188364</v>
       </c>
-      <c r="S40" t="e">
-        <v>#N/A</v>
+      <c r="S40" t="n">
+        <v>3</v>
       </c>
       <c r="T40" t="e">
         <v>#N/A</v>
@@ -6782,37 +7099,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA40" t="s">
         <v>278</v>
       </c>
-      <c r="AB40" t="e">
-        <v>#N/A</v>
+      <c r="AB40" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF40" t="e">
-        <v>#N/A</v>
+      <c r="AD40" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG40" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH40" t="s">
-        <v>360</v>
-      </c>
-      <c r="AI40" t="e">
-        <v>#N/A</v>
+        <v>382</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>383</v>
       </c>
       <c r="AJ40" t="s">
         <v>287</v>
@@ -6820,12 +7137,12 @@
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s">
         <v>271</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" t="s">
         <v>272</v>
       </c>
       <c r="D41" t="s">
@@ -6843,8 +7160,8 @@
       <c r="H41" t="n">
         <v>2.94</v>
       </c>
-      <c r="I41" t="e">
-        <v>#N/A</v>
+      <c r="I41" t="n">
+        <v>0.006</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -6862,7 +7179,7 @@
         <v>-23.67</v>
       </c>
       <c r="O41" t="n">
-        <v>0.314</v>
+        <v>0.222031529292576</v>
       </c>
       <c r="P41" t="e">
         <v>#N/A</v>
@@ -6873,8 +7190,8 @@
       <c r="R41" s="11" t="n">
         <v>27.9582391479917</v>
       </c>
-      <c r="S41" t="e">
-        <v>#N/A</v>
+      <c r="S41" t="n">
+        <v>3</v>
       </c>
       <c r="T41" t="e">
         <v>#N/A</v>
@@ -6892,37 +7209,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA41" t="s">
         <v>278</v>
       </c>
-      <c r="AB41" t="e">
-        <v>#N/A</v>
+      <c r="AB41" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF41" t="e">
-        <v>#N/A</v>
+      <c r="AD41" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG41" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH41" t="s">
-        <v>362</v>
-      </c>
-      <c r="AI41" t="e">
-        <v>#N/A</v>
+        <v>385</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>386</v>
       </c>
       <c r="AJ41" t="s">
         <v>287</v>
@@ -6930,12 +7247,12 @@
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="B42" t="s">
         <v>271</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C42" t="s">
         <v>272</v>
       </c>
       <c r="D42" t="s">
@@ -6953,8 +7270,8 @@
       <c r="H42" t="n">
         <v>3.082</v>
       </c>
-      <c r="I42" t="e">
-        <v>#N/A</v>
+      <c r="I42" t="n">
+        <v>0.015</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -6972,7 +7289,7 @@
         <v>-24.2505</v>
       </c>
       <c r="O42" t="n">
-        <v>0.305999999999998</v>
+        <v>0.216374675043082</v>
       </c>
       <c r="P42" t="e">
         <v>#N/A</v>
@@ -6983,8 +7300,8 @@
       <c r="R42" s="11" t="n">
         <v>27.959494062997</v>
       </c>
-      <c r="S42" t="e">
-        <v>#N/A</v>
+      <c r="S42" t="n">
+        <v>3</v>
       </c>
       <c r="T42" t="e">
         <v>#N/A</v>
@@ -7002,37 +7319,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA42" t="s">
         <v>278</v>
       </c>
-      <c r="AB42" t="e">
-        <v>#N/A</v>
+      <c r="AB42" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF42" t="e">
-        <v>#N/A</v>
+      <c r="AD42" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG42" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH42" t="s">
-        <v>364</v>
-      </c>
-      <c r="AI42" t="e">
-        <v>#N/A</v>
+        <v>388</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>389</v>
       </c>
       <c r="AJ42" t="s">
         <v>287</v>
@@ -7040,12 +7357,12 @@
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="B43" t="s">
         <v>271</v>
       </c>
-      <c r="C43" s="34" t="s">
+      <c r="C43" t="s">
         <v>272</v>
       </c>
       <c r="D43" t="s">
@@ -7063,8 +7380,8 @@
       <c r="H43" t="n">
         <v>3.1313</v>
       </c>
-      <c r="I43" t="e">
-        <v>#N/A</v>
+      <c r="I43" t="n">
+        <v>0.015</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -7082,7 +7399,7 @@
         <v>-23.8645</v>
       </c>
       <c r="O43" t="n">
-        <v>0.298000000000002</v>
+        <v>0.210717820793592</v>
       </c>
       <c r="P43" t="e">
         <v>#N/A</v>
@@ -7093,8 +7410,8 @@
       <c r="R43" s="11" t="n">
         <v>27.9788796459693</v>
       </c>
-      <c r="S43" t="e">
-        <v>#N/A</v>
+      <c r="S43" t="n">
+        <v>3</v>
       </c>
       <c r="T43" t="e">
         <v>#N/A</v>
@@ -7112,37 +7429,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA43" t="s">
         <v>278</v>
       </c>
-      <c r="AB43" t="e">
-        <v>#N/A</v>
+      <c r="AB43" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF43" t="e">
-        <v>#N/A</v>
+      <c r="AD43" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG43" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH43" t="s">
-        <v>366</v>
-      </c>
-      <c r="AI43" t="e">
-        <v>#N/A</v>
+        <v>391</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>392</v>
       </c>
       <c r="AJ43" t="s">
         <v>287</v>
@@ -7150,12 +7467,12 @@
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s">
         <v>271</v>
       </c>
-      <c r="C44" s="34" t="s">
+      <c r="C44" t="s">
         <v>272</v>
       </c>
       <c r="D44" t="s">
@@ -7173,8 +7490,8 @@
       <c r="H44" t="n">
         <v>3.321</v>
       </c>
-      <c r="I44" t="e">
-        <v>#N/A</v>
+      <c r="I44" t="n">
+        <v>0.015</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -7192,7 +7509,7 @@
         <v>-24.33</v>
       </c>
       <c r="O44" t="n">
-        <v>0.120000000000005</v>
+        <v>0.0848528137423889</v>
       </c>
       <c r="P44" t="e">
         <v>#N/A</v>
@@ -7203,8 +7520,8 @@
       <c r="R44" s="11" t="n">
         <v>28.0367741010069</v>
       </c>
-      <c r="S44" t="e">
-        <v>#N/A</v>
+      <c r="S44" t="n">
+        <v>3</v>
       </c>
       <c r="T44" t="e">
         <v>#N/A</v>
@@ -7222,37 +7539,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA44" t="s">
         <v>278</v>
       </c>
-      <c r="AB44" t="e">
-        <v>#N/A</v>
+      <c r="AB44" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF44" t="e">
-        <v>#N/A</v>
+      <c r="AD44" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG44" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH44" t="s">
-        <v>368</v>
-      </c>
-      <c r="AI44" t="e">
-        <v>#N/A</v>
+        <v>394</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>395</v>
       </c>
       <c r="AJ44" t="s">
         <v>287</v>
@@ -7260,12 +7577,12 @@
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="B45" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="34" t="s">
+      <c r="C45" t="s">
         <v>272</v>
       </c>
       <c r="D45" t="s">
@@ -7283,8 +7600,8 @@
       <c r="H45" t="n">
         <v>3.364</v>
       </c>
-      <c r="I45" t="e">
-        <v>#N/A</v>
+      <c r="I45" t="n">
+        <v>0.015</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -7302,7 +7619,7 @@
         <v>-24.2885</v>
       </c>
       <c r="O45" t="n">
-        <v>0.332</v>
+        <v>0.234759451353934</v>
       </c>
       <c r="P45" t="e">
         <v>#N/A</v>
@@ -7313,8 +7630,8 @@
       <c r="R45" s="11" t="n">
         <v>27.5094092724905</v>
       </c>
-      <c r="S45" t="e">
-        <v>#N/A</v>
+      <c r="S45" t="n">
+        <v>3</v>
       </c>
       <c r="T45" t="e">
         <v>#N/A</v>
@@ -7332,37 +7649,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA45" t="s">
         <v>278</v>
       </c>
-      <c r="AB45" t="e">
-        <v>#N/A</v>
+      <c r="AB45" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF45" t="e">
-        <v>#N/A</v>
+      <c r="AD45" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG45" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH45" t="s">
-        <v>370</v>
-      </c>
-      <c r="AI45" t="e">
-        <v>#N/A</v>
+        <v>397</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>398</v>
       </c>
       <c r="AJ45" t="s">
         <v>287</v>
@@ -7370,12 +7687,12 @@
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="B46" t="s">
         <v>271</v>
       </c>
-      <c r="C46" s="34" t="s">
+      <c r="C46" t="s">
         <v>272</v>
       </c>
       <c r="D46" t="s">
@@ -7393,8 +7710,8 @@
       <c r="H46" t="n">
         <v>3.457</v>
       </c>
-      <c r="I46" t="e">
-        <v>#N/A</v>
+      <c r="I46" t="n">
+        <v>0.015</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -7412,7 +7729,7 @@
         <v>-24.2095</v>
       </c>
       <c r="O46" t="n">
-        <v>0.00800000000000268</v>
+        <v>0.00565685424949427</v>
       </c>
       <c r="P46" t="e">
         <v>#N/A</v>
@@ -7423,8 +7740,8 @@
       <c r="R46" s="11" t="n">
         <v>28.0486454971072</v>
       </c>
-      <c r="S46" t="e">
-        <v>#N/A</v>
+      <c r="S46" t="n">
+        <v>3</v>
       </c>
       <c r="T46" t="e">
         <v>#N/A</v>
@@ -7442,37 +7759,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA46" t="s">
         <v>278</v>
       </c>
-      <c r="AB46" t="e">
-        <v>#N/A</v>
+      <c r="AB46" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF46" t="e">
-        <v>#N/A</v>
+      <c r="AD46" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG46" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH46" t="s">
-        <v>372</v>
-      </c>
-      <c r="AI46" t="e">
-        <v>#N/A</v>
+        <v>400</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>401</v>
       </c>
       <c r="AJ46" t="s">
         <v>287</v>
@@ -7480,12 +7797,12 @@
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" t="s">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="B47" t="s">
         <v>271</v>
       </c>
-      <c r="C47" s="34" t="s">
+      <c r="C47" t="s">
         <v>272</v>
       </c>
       <c r="D47" t="s">
@@ -7503,8 +7820,8 @@
       <c r="H47" t="n">
         <v>3.51</v>
       </c>
-      <c r="I47" t="e">
-        <v>#N/A</v>
+      <c r="I47" t="n">
+        <v>0.015</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -7522,7 +7839,7 @@
         <v>-25.08375</v>
       </c>
       <c r="O47" t="n">
-        <v>1.24052717288514</v>
+        <v>0.877185176193258</v>
       </c>
       <c r="P47" t="e">
         <v>#N/A</v>
@@ -7533,8 +7850,8 @@
       <c r="R47" s="11" t="n">
         <v>27.8118248104207</v>
       </c>
-      <c r="S47" t="e">
-        <v>#N/A</v>
+      <c r="S47" t="n">
+        <v>3</v>
       </c>
       <c r="T47" t="e">
         <v>#N/A</v>
@@ -7552,28 +7869,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA47" t="s">
         <v>278</v>
       </c>
-      <c r="AB47" t="e">
-        <v>#N/A</v>
+      <c r="AB47" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF47" t="e">
-        <v>#N/A</v>
+      <c r="AD47" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG47" t="e">
         <v>#N/A</v>
@@ -7581,21 +7898,21 @@
       <c r="AH47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI47" t="e">
-        <v>#N/A</v>
+      <c r="AI47" t="s">
+        <v>403</v>
       </c>
       <c r="AJ47" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="B48" t="s">
         <v>271</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="C48" t="s">
         <v>272</v>
       </c>
       <c r="D48" t="s">
@@ -7613,8 +7930,8 @@
       <c r="H48" t="n">
         <v>3.522</v>
       </c>
-      <c r="I48" t="e">
-        <v>#N/A</v>
+      <c r="I48" t="n">
+        <v>0.015</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -7632,7 +7949,7 @@
         <v>-24.4115</v>
       </c>
       <c r="O48" t="n">
-        <v>0.867999999999994</v>
+        <v>0.61376868606992</v>
       </c>
       <c r="P48" t="e">
         <v>#N/A</v>
@@ -7643,8 +7960,8 @@
       <c r="R48" s="11" t="n">
         <v>28.0147653286189</v>
       </c>
-      <c r="S48" t="e">
-        <v>#N/A</v>
+      <c r="S48" t="n">
+        <v>3</v>
       </c>
       <c r="T48" t="e">
         <v>#N/A</v>
@@ -7662,37 +7979,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA48" t="s">
         <v>278</v>
       </c>
-      <c r="AB48" t="e">
-        <v>#N/A</v>
+      <c r="AB48" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF48" t="e">
-        <v>#N/A</v>
+      <c r="AD48" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG48" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH48" t="s">
-        <v>376</v>
-      </c>
-      <c r="AI48" t="e">
-        <v>#N/A</v>
+        <v>406</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>407</v>
       </c>
       <c r="AJ48" t="s">
         <v>287</v>
@@ -7700,12 +8017,12 @@
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s">
         <v>271</v>
       </c>
-      <c r="C49" s="34" t="s">
+      <c r="C49" t="s">
         <v>272</v>
       </c>
       <c r="D49" t="s">
@@ -7723,8 +8040,8 @@
       <c r="H49" t="n">
         <v>3.673</v>
       </c>
-      <c r="I49" t="e">
-        <v>#N/A</v>
+      <c r="I49" t="n">
+        <v>0.015</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -7741,8 +8058,8 @@
       <c r="N49" t="n">
         <v>-24.59</v>
       </c>
-      <c r="O49" t="e">
-        <v>#N/A</v>
+      <c r="O49" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P49" t="e">
         <v>#N/A</v>
@@ -7753,8 +8070,8 @@
       <c r="R49" s="11" t="n">
         <v>27.8211567922097</v>
       </c>
-      <c r="S49" t="e">
-        <v>#N/A</v>
+      <c r="S49" t="n">
+        <v>3</v>
       </c>
       <c r="T49" t="e">
         <v>#N/A</v>
@@ -7772,37 +8089,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA49" t="s">
         <v>278</v>
       </c>
-      <c r="AB49" t="e">
-        <v>#N/A</v>
+      <c r="AB49" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF49" t="e">
-        <v>#N/A</v>
+      <c r="AD49" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG49" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH49" t="s">
-        <v>378</v>
-      </c>
-      <c r="AI49" t="e">
-        <v>#N/A</v>
+        <v>409</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>410</v>
       </c>
       <c r="AJ49" t="s">
         <v>287</v>
@@ -7810,12 +8127,12 @@
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="B50" t="s">
         <v>271</v>
       </c>
-      <c r="C50" s="34" t="s">
+      <c r="C50" t="s">
         <v>272</v>
       </c>
       <c r="D50" t="s">
@@ -7833,8 +8150,8 @@
       <c r="H50" t="n">
         <v>3.8485</v>
       </c>
-      <c r="I50" t="e">
-        <v>#N/A</v>
+      <c r="I50" t="n">
+        <v>0.015</v>
       </c>
       <c r="J50" t="e">
         <v>#N/A</v>
@@ -7852,7 +8169,7 @@
         <v>-23.8875</v>
       </c>
       <c r="O50" t="n">
-        <v>0.398000000000004</v>
+        <v>0.281428498912248</v>
       </c>
       <c r="P50" t="e">
         <v>#N/A</v>
@@ -7863,8 +8180,8 @@
       <c r="R50" s="11" t="n">
         <v>28.0477761264967</v>
       </c>
-      <c r="S50" t="e">
-        <v>#N/A</v>
+      <c r="S50" t="n">
+        <v>3</v>
       </c>
       <c r="T50" t="e">
         <v>#N/A</v>
@@ -7882,37 +8199,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA50" t="s">
         <v>278</v>
       </c>
-      <c r="AB50" t="e">
-        <v>#N/A</v>
+      <c r="AB50" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF50" t="e">
-        <v>#N/A</v>
+      <c r="AD50" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG50" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH50" t="s">
-        <v>380</v>
-      </c>
-      <c r="AI50" t="e">
-        <v>#N/A</v>
+        <v>412</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>413</v>
       </c>
       <c r="AJ50" t="s">
         <v>287</v>
@@ -7920,12 +8237,12 @@
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" t="s">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="B51" t="s">
         <v>271</v>
       </c>
-      <c r="C51" s="34" t="s">
+      <c r="C51" t="s">
         <v>272</v>
       </c>
       <c r="D51" t="s">
@@ -7943,8 +8260,8 @@
       <c r="H51" t="n">
         <v>3.9855</v>
       </c>
-      <c r="I51" t="e">
-        <v>#N/A</v>
+      <c r="I51" t="n">
+        <v>0.015</v>
       </c>
       <c r="J51" t="e">
         <v>#N/A</v>
@@ -7962,7 +8279,7 @@
         <v>-24.1325</v>
       </c>
       <c r="O51" t="n">
-        <v>0.285999999999994</v>
+        <v>0.202232539419349</v>
       </c>
       <c r="P51" t="e">
         <v>#N/A</v>
@@ -7973,8 +8290,8 @@
       <c r="R51" s="11" t="n">
         <v>28.0165447664211</v>
       </c>
-      <c r="S51" t="e">
-        <v>#N/A</v>
+      <c r="S51" t="n">
+        <v>3</v>
       </c>
       <c r="T51" t="e">
         <v>#N/A</v>
@@ -7992,37 +8309,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA51" t="s">
         <v>278</v>
       </c>
-      <c r="AB51" t="e">
-        <v>#N/A</v>
+      <c r="AB51" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF51" t="e">
-        <v>#N/A</v>
+      <c r="AD51" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG51" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH51" t="s">
-        <v>382</v>
-      </c>
-      <c r="AI51" t="e">
-        <v>#N/A</v>
+        <v>415</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>416</v>
       </c>
       <c r="AJ51" t="s">
         <v>287</v>
@@ -8030,12 +8347,12 @@
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="B52" t="s">
         <v>271</v>
       </c>
-      <c r="C52" s="34" t="s">
+      <c r="C52" t="s">
         <v>272</v>
       </c>
       <c r="D52" t="s">
@@ -8053,8 +8370,8 @@
       <c r="H52" t="n">
         <v>4.1062</v>
       </c>
-      <c r="I52" t="e">
-        <v>#N/A</v>
+      <c r="I52" t="n">
+        <v>0.03</v>
       </c>
       <c r="J52" t="e">
         <v>#N/A</v>
@@ -8071,8 +8388,8 @@
       <c r="N52" t="n">
         <v>-24.67</v>
       </c>
-      <c r="O52" t="e">
-        <v>#N/A</v>
+      <c r="O52" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P52" t="e">
         <v>#N/A</v>
@@ -8083,8 +8400,8 @@
       <c r="R52" s="11" t="n">
         <v>28.0662709552077</v>
       </c>
-      <c r="S52" t="e">
-        <v>#N/A</v>
+      <c r="S52" t="n">
+        <v>3</v>
       </c>
       <c r="T52" t="e">
         <v>#N/A</v>
@@ -8102,37 +8419,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA52" t="s">
         <v>278</v>
       </c>
-      <c r="AB52" t="e">
-        <v>#N/A</v>
+      <c r="AB52" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF52" t="e">
-        <v>#N/A</v>
+      <c r="AD52" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG52" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH52" t="s">
-        <v>384</v>
-      </c>
-      <c r="AI52" t="e">
-        <v>#N/A</v>
+        <v>418</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>419</v>
       </c>
       <c r="AJ52" t="s">
         <v>287</v>
@@ -8140,12 +8457,12 @@
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" t="s">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="B53" t="s">
         <v>271</v>
       </c>
-      <c r="C53" s="34" t="s">
+      <c r="C53" t="s">
         <v>272</v>
       </c>
       <c r="D53" t="s">
@@ -8163,8 +8480,8 @@
       <c r="H53" t="n">
         <v>4.4475</v>
       </c>
-      <c r="I53" t="e">
-        <v>#N/A</v>
+      <c r="I53" t="n">
+        <v>0.03</v>
       </c>
       <c r="J53" t="e">
         <v>#N/A</v>
@@ -8182,7 +8499,7 @@
         <v>-25.547</v>
       </c>
       <c r="O53" t="n">
-        <v>0.358000000000004</v>
+        <v>0.253144227664787</v>
       </c>
       <c r="P53" t="e">
         <v>#N/A</v>
@@ -8193,8 +8510,8 @@
       <c r="R53" s="11" t="n">
         <v>28.2647058823529</v>
       </c>
-      <c r="S53" t="e">
-        <v>#N/A</v>
+      <c r="S53" t="n">
+        <v>3</v>
       </c>
       <c r="T53" t="e">
         <v>#N/A</v>
@@ -8212,37 +8529,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA53" t="s">
         <v>278</v>
       </c>
-      <c r="AB53" t="e">
-        <v>#N/A</v>
+      <c r="AB53" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF53" t="e">
-        <v>#N/A</v>
+      <c r="AD53" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG53" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH53" t="s">
-        <v>386</v>
-      </c>
-      <c r="AI53" t="e">
-        <v>#N/A</v>
+        <v>421</v>
+      </c>
+      <c r="AI53" t="s">
+        <v>422</v>
       </c>
       <c r="AJ53" t="s">
         <v>287</v>
@@ -8250,12 +8567,12 @@
     </row>
     <row r="54" ht="19" customHeight="1">
       <c r="A54" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s">
         <v>271</v>
       </c>
-      <c r="C54" s="34" t="s">
+      <c r="C54" t="s">
         <v>272</v>
       </c>
       <c r="D54" t="s">
@@ -8273,8 +8590,8 @@
       <c r="H54" t="n">
         <v>4.7762</v>
       </c>
-      <c r="I54" t="e">
-        <v>#N/A</v>
+      <c r="I54" t="n">
+        <v>0.03</v>
       </c>
       <c r="J54" t="e">
         <v>#N/A</v>
@@ -8292,7 +8609,7 @@
         <v>-25.074</v>
       </c>
       <c r="O54" t="n">
-        <v>0.354</v>
+        <v>0.250315800540037</v>
       </c>
       <c r="P54" t="e">
         <v>#N/A</v>
@@ -8303,8 +8620,8 @@
       <c r="R54" s="11" t="n">
         <v>28.089094513497</v>
       </c>
-      <c r="S54" t="e">
-        <v>#N/A</v>
+      <c r="S54" t="n">
+        <v>3</v>
       </c>
       <c r="T54" t="e">
         <v>#N/A</v>
@@ -8322,37 +8639,37 @@
         <v>#N/A</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA54" t="s">
         <v>278</v>
       </c>
-      <c r="AB54" t="e">
-        <v>#N/A</v>
+      <c r="AB54" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF54" t="e">
-        <v>#N/A</v>
+      <c r="AD54" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG54" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH54" t="s">
-        <v>388</v>
-      </c>
-      <c r="AI54" t="e">
-        <v>#N/A</v>
+        <v>424</v>
+      </c>
+      <c r="AI54" t="s">
+        <v>425</v>
       </c>
       <c r="AJ54" t="s">
         <v>287</v>
@@ -8360,12 +8677,12 @@
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" t="s">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="B55" t="s">
         <v>271</v>
       </c>
-      <c r="C55" s="34" t="s">
+      <c r="C55" t="s">
         <v>272</v>
       </c>
       <c r="D55" t="s">
@@ -8383,8 +8700,8 @@
       <c r="H55" t="n">
         <v>7.15</v>
       </c>
-      <c r="I55" t="e">
-        <v>#N/A</v>
+      <c r="I55" t="n">
+        <v>0.0374740887686478</v>
       </c>
       <c r="J55" t="e">
         <v>#N/A</v>
@@ -8402,7 +8719,7 @@
         <v>-24.264</v>
       </c>
       <c r="O55" t="n">
-        <v>0.89757153846697</v>
+        <v>0.634678921450036</v>
       </c>
       <c r="P55" t="e">
         <v>#N/A</v>
@@ -8413,8 +8730,8 @@
       <c r="R55" s="11" t="n">
         <v>27.8494779640157</v>
       </c>
-      <c r="S55" t="e">
-        <v>#N/A</v>
+      <c r="S55" t="n">
+        <v>3</v>
       </c>
       <c r="T55" t="e">
         <v>#N/A</v>
@@ -8432,28 +8749,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA55" t="s">
         <v>278</v>
       </c>
-      <c r="AB55" t="e">
-        <v>#N/A</v>
+      <c r="AB55" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF55" t="e">
-        <v>#N/A</v>
+      <c r="AD55" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG55" t="e">
         <v>#N/A</v>
@@ -8461,21 +8778,21 @@
       <c r="AH55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI55" t="e">
-        <v>#N/A</v>
+      <c r="AI55" t="s">
+        <v>427</v>
       </c>
       <c r="AJ55" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s">
         <v>271</v>
       </c>
-      <c r="C56" s="34" t="s">
+      <c r="C56" t="s">
         <v>272</v>
       </c>
       <c r="D56" t="s">
@@ -8493,8 +8810,8 @@
       <c r="H56" t="n">
         <v>14.1</v>
       </c>
-      <c r="I56" t="e">
-        <v>#N/A</v>
+      <c r="I56" t="n">
+        <v>0.0713456756295306</v>
       </c>
       <c r="J56" t="e">
         <v>#N/A</v>
@@ -8512,7 +8829,7 @@
         <v>-23.00275</v>
       </c>
       <c r="O56" t="n">
-        <v>0.931160387187106</v>
+        <v>0.658429824152293</v>
       </c>
       <c r="P56" t="e">
         <v>#N/A</v>
@@ -8523,8 +8840,8 @@
       <c r="R56" s="11" t="n">
         <v>27.4265654150436</v>
       </c>
-      <c r="S56" t="e">
-        <v>#N/A</v>
+      <c r="S56" t="n">
+        <v>3</v>
       </c>
       <c r="T56" t="e">
         <v>#N/A</v>
@@ -8542,28 +8859,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA56" t="s">
         <v>278</v>
       </c>
-      <c r="AB56" t="e">
-        <v>#N/A</v>
+      <c r="AB56" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF56" t="e">
-        <v>#N/A</v>
+      <c r="AD56" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG56" t="e">
         <v>#N/A</v>
@@ -8571,21 +8888,21 @@
       <c r="AH56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI56" t="e">
-        <v>#N/A</v>
+      <c r="AI56" t="s">
+        <v>429</v>
       </c>
       <c r="AJ56" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" t="s">
-        <v>391</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" t="s">
         <v>272</v>
       </c>
       <c r="D57" t="s">
@@ -8603,8 +8920,8 @@
       <c r="H57" t="n">
         <v>14.74</v>
       </c>
-      <c r="I57" t="e">
-        <v>#N/A</v>
+      <c r="I57" t="n">
+        <v>0.074412758844237</v>
       </c>
       <c r="J57" t="e">
         <v>#N/A</v>
@@ -8622,7 +8939,7 @@
         <v>-25.2965</v>
       </c>
       <c r="O57" t="n">
-        <v>1.00267741572201</v>
+        <v>0.708999999999636</v>
       </c>
       <c r="P57" t="e">
         <v>#N/A</v>
@@ -8633,8 +8950,8 @@
       <c r="R57" s="11" t="n">
         <v>28.0543395321161</v>
       </c>
-      <c r="S57" t="e">
-        <v>#N/A</v>
+      <c r="S57" t="n">
+        <v>3</v>
       </c>
       <c r="T57" t="e">
         <v>#N/A</v>
@@ -8652,28 +8969,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA57" t="s">
         <v>278</v>
       </c>
-      <c r="AB57" t="e">
-        <v>#N/A</v>
+      <c r="AB57" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF57" t="e">
-        <v>#N/A</v>
+      <c r="AD57" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG57" t="e">
         <v>#N/A</v>
@@ -8685,17 +9002,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ57" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" t="s">
-        <v>392</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s">
         <v>271</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" t="s">
         <v>272</v>
       </c>
       <c r="D58" t="s">
@@ -8713,8 +9030,8 @@
       <c r="H58" t="n">
         <v>15.1</v>
       </c>
-      <c r="I58" t="e">
-        <v>#N/A</v>
+      <c r="I58" t="n">
+        <v>0.0761349442044506</v>
       </c>
       <c r="J58" t="e">
         <v>#N/A</v>
@@ -8795,17 +9112,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ58" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" t="s">
-        <v>393</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s">
         <v>271</v>
       </c>
-      <c r="C59" s="34" t="s">
+      <c r="C59" t="s">
         <v>272</v>
       </c>
       <c r="D59" t="s">
@@ -8823,8 +9140,8 @@
       <c r="H59" t="n">
         <v>15.84</v>
       </c>
-      <c r="I59" t="e">
-        <v>#N/A</v>
+      <c r="I59" t="n">
+        <v>0.0796683736276814</v>
       </c>
       <c r="J59" t="e">
         <v>#N/A</v>
@@ -8842,7 +9159,7 @@
         <v>-24.539</v>
       </c>
       <c r="O59" t="n">
-        <v>0.260637679547682</v>
+        <v>0.184298670640892</v>
       </c>
       <c r="P59" t="e">
         <v>#N/A</v>
@@ -8851,10 +9168,10 @@
         <v>#N/A</v>
       </c>
       <c r="R59" s="11" t="n">
-        <v>29.3399882523485</v>
-      </c>
-      <c r="S59" t="e">
-        <v>#N/A</v>
+        <v>28.7178228307022</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5.22015325445528</v>
       </c>
       <c r="T59" t="e">
         <v>#N/A</v>
@@ -8863,7 +9180,7 @@
         <v>#N/A</v>
       </c>
       <c r="V59" s="11" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="W59" t="n">
         <v>0.2</v>
@@ -8872,28 +9189,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA59" t="s">
         <v>278</v>
       </c>
-      <c r="AB59" t="e">
-        <v>#N/A</v>
+      <c r="AB59" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF59" t="e">
-        <v>#N/A</v>
+      <c r="AD59" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG59" t="e">
         <v>#N/A</v>
@@ -8905,17 +9222,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ59" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" t="s">
-        <v>395</v>
+        <v>434</v>
       </c>
       <c r="B60" t="s">
         <v>271</v>
       </c>
-      <c r="C60" s="34" t="s">
+      <c r="C60" t="s">
         <v>272</v>
       </c>
       <c r="D60" t="s">
@@ -8933,8 +9250,8 @@
       <c r="H60" t="n">
         <v>16.82</v>
       </c>
-      <c r="I60" t="e">
-        <v>#N/A</v>
+      <c r="I60" t="n">
+        <v>0.0843346986615206</v>
       </c>
       <c r="J60" t="e">
         <v>#N/A</v>
@@ -8952,7 +9269,7 @@
         <v>-24.8525</v>
       </c>
       <c r="O60" t="n">
-        <v>0.743405676599464</v>
+        <v>0.525667195096055</v>
       </c>
       <c r="P60" t="e">
         <v>#N/A</v>
@@ -8961,10 +9278,10 @@
         <v>#N/A</v>
       </c>
       <c r="R60" s="11" t="n">
-        <v>28.4949364000287</v>
-      </c>
-      <c r="S60" t="e">
-        <v>#N/A</v>
+        <v>28.3242981568146</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5.22015325445528</v>
       </c>
       <c r="T60" t="e">
         <v>#N/A</v>
@@ -8973,7 +9290,7 @@
         <v>#N/A</v>
       </c>
       <c r="V60" s="11" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="W60" t="n">
         <v>0.2</v>
@@ -8982,28 +9299,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA60" t="s">
         <v>278</v>
       </c>
-      <c r="AB60" t="e">
-        <v>#N/A</v>
+      <c r="AB60" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF60" t="e">
-        <v>#N/A</v>
+      <c r="AD60" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG60" t="e">
         <v>#N/A</v>
@@ -9015,17 +9332,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ60" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s">
         <v>271</v>
       </c>
-      <c r="C61" s="34" t="s">
+      <c r="C61" t="s">
         <v>272</v>
       </c>
       <c r="D61" t="s">
@@ -9043,8 +9360,8 @@
       <c r="H61" t="n">
         <v>18.26</v>
       </c>
-      <c r="I61" t="e">
-        <v>#N/A</v>
+      <c r="I61" t="n">
+        <v>0.0911660473180407</v>
       </c>
       <c r="J61" t="e">
         <v>#N/A</v>
@@ -9062,7 +9379,7 @@
         <v>-24.9545</v>
       </c>
       <c r="O61" t="n">
-        <v>0.179605122421387</v>
+        <v>0.127000000000002</v>
       </c>
       <c r="P61" t="e">
         <v>#N/A</v>
@@ -9071,10 +9388,10 @@
         <v>#N/A</v>
       </c>
       <c r="R61" s="11" t="n">
-        <v>29.4973464705046</v>
-      </c>
-      <c r="S61" t="e">
-        <v>#N/A</v>
+        <v>28.807827651915</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5.22015325445528</v>
       </c>
       <c r="T61" t="e">
         <v>#N/A</v>
@@ -9083,7 +9400,7 @@
         <v>#N/A</v>
       </c>
       <c r="V61" s="11" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="W61" t="n">
         <v>0.2</v>
@@ -9092,28 +9409,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA61" t="s">
         <v>278</v>
       </c>
-      <c r="AB61" t="e">
-        <v>#N/A</v>
+      <c r="AB61" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF61" t="e">
-        <v>#N/A</v>
+      <c r="AD61" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG61" t="e">
         <v>#N/A</v>
@@ -9125,17 +9442,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ61" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="B62" t="s">
         <v>271</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="C62" t="s">
         <v>272</v>
       </c>
       <c r="D62" t="s">
@@ -9153,8 +9470,8 @@
       <c r="H62" t="n">
         <v>20.3</v>
       </c>
-      <c r="I62" t="e">
-        <v>#N/A</v>
+      <c r="I62" t="n">
+        <v>0.100796588972055</v>
       </c>
       <c r="J62" t="e">
         <v>#N/A</v>
@@ -9172,7 +9489,7 @@
         <v>-23.635</v>
       </c>
       <c r="O62" t="n">
-        <v>0.0934380365090494</v>
+        <v>0.066070669236305</v>
       </c>
       <c r="P62" t="e">
         <v>#N/A</v>
@@ -9181,10 +9498,10 @@
         <v>#N/A</v>
       </c>
       <c r="R62" s="11" t="n">
-        <v>28.8455979661833</v>
-      </c>
-      <c r="S62" t="e">
-        <v>#N/A</v>
+        <v>28.4751336975392</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5.22015325445528</v>
       </c>
       <c r="T62" t="e">
         <v>#N/A</v>
@@ -9193,7 +9510,7 @@
         <v>#N/A</v>
       </c>
       <c r="V62" s="11" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="W62" t="n">
         <v>0.2</v>
@@ -9202,50 +9519,50 @@
         <v>#N/A</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA62" t="s">
         <v>278</v>
       </c>
-      <c r="AB62" t="e">
-        <v>#N/A</v>
+      <c r="AB62" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF62" t="e">
-        <v>#N/A</v>
+      <c r="AD62" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG62" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH62" t="s">
-        <v>398</v>
+        <v>437</v>
       </c>
       <c r="AI62" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ62" t="s">
-        <v>399</v>
+        <v>438</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
       <c r="A63" t="s">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="B63" t="s">
         <v>271</v>
       </c>
-      <c r="C63" s="34" t="s">
+      <c r="C63" t="s">
         <v>272</v>
       </c>
       <c r="D63" t="s">
@@ -9263,8 +9580,8 @@
       <c r="H63" t="n">
         <v>22.94</v>
       </c>
-      <c r="I63" t="e">
-        <v>#N/A</v>
+      <c r="I63" t="n">
+        <v>0.1131860143132</v>
       </c>
       <c r="J63" t="e">
         <v>#N/A</v>
@@ -9282,7 +9599,7 @@
         <v>-26.19675</v>
       </c>
       <c r="O63" t="n">
-        <v>0.591631360448454</v>
+        <v>0.418346546935725</v>
       </c>
       <c r="P63" t="e">
         <v>#N/A</v>
@@ -9291,10 +9608,10 @@
         <v>#N/A</v>
       </c>
       <c r="R63" s="11" t="n">
-        <v>29.0620382170888</v>
-      </c>
-      <c r="S63" t="e">
-        <v>#N/A</v>
+        <v>28.5915669403323</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5.22015325445528</v>
       </c>
       <c r="T63" t="e">
         <v>#N/A</v>
@@ -9303,7 +9620,7 @@
         <v>#N/A</v>
       </c>
       <c r="V63" s="11" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="W63" t="n">
         <v>0.2</v>
@@ -9312,161 +9629,3341 @@
         <v>#N/A</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA63" t="s">
         <v>278</v>
       </c>
-      <c r="AB63" t="e">
-        <v>#N/A</v>
+      <c r="AB63" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC63" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF63" t="e">
-        <v>#N/A</v>
+      <c r="AD63" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG63" t="e">
         <v>#N/A</v>
       </c>
       <c r="AH63" t="s">
-        <v>401</v>
+        <v>440</v>
       </c>
       <c r="AI63" t="e">
         <v>#N/A</v>
       </c>
       <c r="AJ63" t="s">
-        <v>399</v>
+        <v>438</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
-      <c r="R64" s="11"/>
-      <c r="V64" s="11"/>
+      <c r="A64" t="s">
+        <v>441</v>
+      </c>
+      <c r="B64" t="s">
+        <v>271</v>
+      </c>
+      <c r="C64" t="s">
+        <v>272</v>
+      </c>
+      <c r="D64" t="s">
+        <v>273</v>
+      </c>
+      <c r="E64" t="s">
+        <v>274</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H64" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.11571083398098</v>
+      </c>
+      <c r="J64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L64" t="s">
+        <v>275</v>
+      </c>
+      <c r="M64" t="s">
+        <v>276</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-25.412</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.590000000000134</v>
+      </c>
+      <c r="P64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R64" s="11" t="n">
+        <v>28.5381376391686</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V64" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH64" t="s">
+        <v>442</v>
+      </c>
+      <c r="AI64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ64" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="65" ht="19" customHeight="1">
-      <c r="R65" s="11"/>
-      <c r="V65" s="11"/>
+      <c r="A65" t="s">
+        <v>443</v>
+      </c>
+      <c r="B65" t="s">
+        <v>271</v>
+      </c>
+      <c r="C65" t="s">
+        <v>272</v>
+      </c>
+      <c r="D65" t="s">
+        <v>273</v>
+      </c>
+      <c r="E65" t="s">
+        <v>274</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H65" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.124198677262932</v>
+      </c>
+      <c r="J65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L65" t="s">
+        <v>275</v>
+      </c>
+      <c r="M65" t="s">
+        <v>276</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-25.90525</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.143212546005345</v>
+      </c>
+      <c r="P65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R65" s="11" t="n">
+        <v>28.5195038690832</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V65" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH65" t="s">
+        <v>444</v>
+      </c>
+      <c r="AI65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="66" ht="19" customHeight="1">
-      <c r="R66" s="11"/>
-      <c r="V66" s="11"/>
+      <c r="A66" t="s">
+        <v>445</v>
+      </c>
+      <c r="B66" t="s">
+        <v>271</v>
+      </c>
+      <c r="C66" t="s">
+        <v>272</v>
+      </c>
+      <c r="D66" t="s">
+        <v>273</v>
+      </c>
+      <c r="E66" t="s">
+        <v>274</v>
+      </c>
+      <c r="F66" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H66" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.130102656493273</v>
+      </c>
+      <c r="J66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L66" t="s">
+        <v>275</v>
+      </c>
+      <c r="M66" t="s">
+        <v>276</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-29.43075</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.495529851102049</v>
+      </c>
+      <c r="P66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R66" s="11" t="n">
+        <v>28.1677285172574</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V66" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH66" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ66" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="67" ht="19" customHeight="1">
-      <c r="R67" s="11"/>
-      <c r="V67" s="11"/>
+      <c r="A67" t="s">
+        <v>447</v>
+      </c>
+      <c r="B67" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" t="s">
+        <v>272</v>
+      </c>
+      <c r="D67" t="s">
+        <v>273</v>
+      </c>
+      <c r="E67" t="s">
+        <v>274</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H67" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.13603834711417</v>
+      </c>
+      <c r="J67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L67" t="s">
+        <v>275</v>
+      </c>
+      <c r="M67" t="s">
+        <v>276</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-29.67025</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.0923498781807529</v>
+      </c>
+      <c r="P67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R67" s="11" t="n">
+        <v>27.8363860371722</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3</v>
+      </c>
+      <c r="T67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V67" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>448</v>
+      </c>
+      <c r="AI67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="68" ht="19" customHeight="1">
-      <c r="R68" s="11"/>
-      <c r="V68" s="11"/>
+      <c r="A68" t="s">
+        <v>449</v>
+      </c>
+      <c r="B68" t="s">
+        <v>271</v>
+      </c>
+      <c r="C68" t="s">
+        <v>272</v>
+      </c>
+      <c r="D68" t="s">
+        <v>273</v>
+      </c>
+      <c r="E68" t="s">
+        <v>274</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H68" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.140342102680961</v>
+      </c>
+      <c r="J68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L68" t="s">
+        <v>275</v>
+      </c>
+      <c r="M68" t="s">
+        <v>276</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-30.326</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.0594474557908068</v>
+      </c>
+      <c r="P68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R68" s="11" t="n">
+        <v>28.1421679783127</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3</v>
+      </c>
+      <c r="T68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V68" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH68" t="s">
+        <v>450</v>
+      </c>
+      <c r="AI68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="69" ht="19" customHeight="1">
-      <c r="R69" s="11"/>
-      <c r="V69" s="11"/>
+      <c r="A69" t="s">
+        <v>451</v>
+      </c>
+      <c r="B69" t="s">
+        <v>271</v>
+      </c>
+      <c r="C69" t="s">
+        <v>272</v>
+      </c>
+      <c r="D69" t="s">
+        <v>273</v>
+      </c>
+      <c r="E69" t="s">
+        <v>274</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H69" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.142329562597652</v>
+      </c>
+      <c r="J69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L69" t="s">
+        <v>275</v>
+      </c>
+      <c r="M69" t="s">
+        <v>276</v>
+      </c>
+      <c r="N69" t="n">
+        <v>-30.78325</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.118329342655714</v>
+      </c>
+      <c r="P69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R69" s="11" t="n">
+        <v>28.6342004977553</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V69" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH69" t="s">
+        <v>452</v>
+      </c>
+      <c r="AI69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ69" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="70" ht="19" customHeight="1">
-      <c r="R70" s="11"/>
-      <c r="V70" s="11"/>
+      <c r="A70" t="s">
+        <v>453</v>
+      </c>
+      <c r="B70" t="s">
+        <v>271</v>
+      </c>
+      <c r="C70" t="s">
+        <v>272</v>
+      </c>
+      <c r="D70" t="s">
+        <v>273</v>
+      </c>
+      <c r="E70" t="s">
+        <v>274</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H70" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.143992316414749</v>
+      </c>
+      <c r="J70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L70" t="s">
+        <v>275</v>
+      </c>
+      <c r="M70" t="s">
+        <v>276</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-31.58175</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.423811868640104</v>
+      </c>
+      <c r="P70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R70" s="11" t="n">
+        <v>28.5186217180448</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V70" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH70" t="s">
+        <v>454</v>
+      </c>
+      <c r="AI70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ70" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="71" ht="19" customHeight="1">
-      <c r="R71" s="11"/>
-      <c r="V71" s="11"/>
+      <c r="A71" t="s">
+        <v>455</v>
+      </c>
+      <c r="B71" t="s">
+        <v>271</v>
+      </c>
+      <c r="C71" t="s">
+        <v>272</v>
+      </c>
+      <c r="D71" t="s">
+        <v>273</v>
+      </c>
+      <c r="E71" t="s">
+        <v>274</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H71" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.144315507504168</v>
+      </c>
+      <c r="J71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L71" t="s">
+        <v>275</v>
+      </c>
+      <c r="M71" t="s">
+        <v>276</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-31.09325</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.0309057707664228</v>
+      </c>
+      <c r="P71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R71" s="11" t="n">
+        <v>29.1054514797129</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V71" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH71" t="s">
+        <v>456</v>
+      </c>
+      <c r="AI71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ71" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="72" ht="19" customHeight="1">
-      <c r="R72" s="11"/>
-      <c r="V72" s="11"/>
+      <c r="A72" t="s">
+        <v>457</v>
+      </c>
+      <c r="B72" t="s">
+        <v>271</v>
+      </c>
+      <c r="C72" t="s">
+        <v>272</v>
+      </c>
+      <c r="D72" t="s">
+        <v>273</v>
+      </c>
+      <c r="E72" t="s">
+        <v>274</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H72" t="n">
+        <v>30.62</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.148836075511329</v>
+      </c>
+      <c r="J72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L72" t="s">
+        <v>275</v>
+      </c>
+      <c r="M72" t="s">
+        <v>276</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-30.4305</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.0623965811029211</v>
+      </c>
+      <c r="P72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R72" s="11" t="n">
+        <v>28.891122869429</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V72" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH72" t="s">
+        <v>458</v>
+      </c>
+      <c r="AI72" t="s">
+        <v>459</v>
+      </c>
+      <c r="AJ72" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="73" ht="19" customHeight="1">
-      <c r="R73" s="11"/>
-      <c r="V73" s="11"/>
+      <c r="A73" t="s">
+        <v>460</v>
+      </c>
+      <c r="B73" t="s">
+        <v>271</v>
+      </c>
+      <c r="C73" t="s">
+        <v>272</v>
+      </c>
+      <c r="D73" t="s">
+        <v>273</v>
+      </c>
+      <c r="E73" t="s">
+        <v>274</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H73" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.151830264768187</v>
+      </c>
+      <c r="J73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L73" t="s">
+        <v>275</v>
+      </c>
+      <c r="M73" t="s">
+        <v>276</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-29.84925</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.148962523251096</v>
+      </c>
+      <c r="P73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R73" s="11" t="n">
+        <v>28.6550526310963</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V73" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH73" t="s">
+        <v>461</v>
+      </c>
+      <c r="AI73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ73" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="74" ht="19" customHeight="1">
-      <c r="R74" s="11"/>
-      <c r="V74" s="11"/>
+      <c r="A74" t="s">
+        <v>462</v>
+      </c>
+      <c r="B74" t="s">
+        <v>271</v>
+      </c>
+      <c r="C74" t="s">
+        <v>272</v>
+      </c>
+      <c r="D74" t="s">
+        <v>273</v>
+      </c>
+      <c r="E74" t="s">
+        <v>274</v>
+      </c>
+      <c r="F74" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H74" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.15537306316801</v>
+      </c>
+      <c r="J74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L74" t="s">
+        <v>275</v>
+      </c>
+      <c r="M74" t="s">
+        <v>276</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-30.00225</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.621945737182709</v>
+      </c>
+      <c r="P74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R74" s="11" t="n">
+        <v>28.8886250727358</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V74" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH74" t="s">
+        <v>463</v>
+      </c>
+      <c r="AI74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ74" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="75" ht="19" customHeight="1">
-      <c r="R75" s="11"/>
-      <c r="V75" s="11"/>
+      <c r="A75" t="s">
+        <v>464</v>
+      </c>
+      <c r="B75" t="s">
+        <v>271</v>
+      </c>
+      <c r="C75" t="s">
+        <v>272</v>
+      </c>
+      <c r="D75" t="s">
+        <v>273</v>
+      </c>
+      <c r="E75" t="s">
+        <v>274</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H75" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.15785498685652</v>
+      </c>
+      <c r="J75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L75" t="s">
+        <v>275</v>
+      </c>
+      <c r="M75" t="s">
+        <v>276</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-29.7665</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.123636564170959</v>
+      </c>
+      <c r="P75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R75" s="11" t="n">
+        <v>29.2953513570497</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V75" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH75" t="s">
+        <v>465</v>
+      </c>
+      <c r="AI75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ75" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="76" ht="19" customHeight="1">
-      <c r="R76" s="11"/>
-      <c r="V76" s="11"/>
+      <c r="A76" t="s">
+        <v>466</v>
+      </c>
+      <c r="B76" t="s">
+        <v>271</v>
+      </c>
+      <c r="C76" t="s">
+        <v>272</v>
+      </c>
+      <c r="D76" t="s">
+        <v>273</v>
+      </c>
+      <c r="E76" t="s">
+        <v>274</v>
+      </c>
+      <c r="F76" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H76" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.159003302011478</v>
+      </c>
+      <c r="J76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L76" t="s">
+        <v>275</v>
+      </c>
+      <c r="M76" t="s">
+        <v>276</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-29.613</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.39202465908791</v>
+      </c>
+      <c r="P76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R76" s="11" t="n">
+        <v>28.9383043680223</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V76" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH76" t="s">
+        <v>467</v>
+      </c>
+      <c r="AI76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ76" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="77" ht="19" customHeight="1">
-      <c r="R77" s="11"/>
-      <c r="V77" s="11"/>
+      <c r="A77" t="s">
+        <v>468</v>
+      </c>
+      <c r="B77" t="s">
+        <v>271</v>
+      </c>
+      <c r="C77" t="s">
+        <v>272</v>
+      </c>
+      <c r="D77" t="s">
+        <v>273</v>
+      </c>
+      <c r="E77" t="s">
+        <v>274</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H77" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.159370667040372</v>
+      </c>
+      <c r="J77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L77" t="s">
+        <v>275</v>
+      </c>
+      <c r="M77" t="s">
+        <v>276</v>
+      </c>
+      <c r="N77" t="n">
+        <v>-29.45975</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.386466686792105</v>
+      </c>
+      <c r="P77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R77" s="11" t="n">
+        <v>28.9215694057445</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V77" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH77" t="s">
+        <v>469</v>
+      </c>
+      <c r="AI77" t="s">
+        <v>470</v>
+      </c>
+      <c r="AJ77" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="78" ht="19" customHeight="1">
-      <c r="R78" s="11"/>
-      <c r="V78" s="11"/>
+      <c r="A78" t="s">
+        <v>471</v>
+      </c>
+      <c r="B78" t="s">
+        <v>271</v>
+      </c>
+      <c r="C78" t="s">
+        <v>272</v>
+      </c>
+      <c r="D78" t="s">
+        <v>273</v>
+      </c>
+      <c r="E78" t="s">
+        <v>274</v>
+      </c>
+      <c r="F78" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H78" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.159646160450451</v>
+      </c>
+      <c r="J78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L78" t="s">
+        <v>275</v>
+      </c>
+      <c r="M78" t="s">
+        <v>276</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-29.244</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.486000000000299</v>
+      </c>
+      <c r="P78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R78" s="11" t="n">
+        <v>28.63166343536</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V78" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH78" t="s">
+        <v>472</v>
+      </c>
+      <c r="AI78" t="s">
+        <v>473</v>
+      </c>
+      <c r="AJ78" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="79" ht="19" customHeight="1">
-      <c r="R79" s="11"/>
-      <c r="V79" s="11"/>
+      <c r="A79" t="s">
+        <v>474</v>
+      </c>
+      <c r="B79" t="s">
+        <v>271</v>
+      </c>
+      <c r="C79" t="s">
+        <v>272</v>
+      </c>
+      <c r="D79" t="s">
+        <v>273</v>
+      </c>
+      <c r="E79" t="s">
+        <v>274</v>
+      </c>
+      <c r="F79" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H79" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.161849176996253</v>
+      </c>
+      <c r="J79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L79" t="s">
+        <v>275</v>
+      </c>
+      <c r="M79" t="s">
+        <v>276</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-29.59825</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.293619651930389</v>
+      </c>
+      <c r="P79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R79" s="11" t="n">
+        <v>28.8625280125032</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V79" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH79" t="s">
+        <v>475</v>
+      </c>
+      <c r="AI79" t="s">
+        <v>476</v>
+      </c>
+      <c r="AJ79" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="80" ht="19" customHeight="1">
-      <c r="R80" s="11"/>
-      <c r="V80" s="11"/>
+      <c r="A80" t="s">
+        <v>477</v>
+      </c>
+      <c r="B80" t="s">
+        <v>271</v>
+      </c>
+      <c r="C80" t="s">
+        <v>272</v>
+      </c>
+      <c r="D80" t="s">
+        <v>273</v>
+      </c>
+      <c r="E80" t="s">
+        <v>274</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H80" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.162399674389343</v>
+      </c>
+      <c r="J80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L80" t="s">
+        <v>275</v>
+      </c>
+      <c r="M80" t="s">
+        <v>276</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-28.50725</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.628929646303796</v>
+      </c>
+      <c r="P80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R80" s="11" t="n">
+        <v>29.2834794789906</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V80" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH80" t="s">
+        <v>478</v>
+      </c>
+      <c r="AI80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ80" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="81" ht="19" customHeight="1">
-      <c r="R81" s="11"/>
-      <c r="V81" s="11"/>
+      <c r="A81" t="s">
+        <v>479</v>
+      </c>
+      <c r="B81" t="s">
+        <v>271</v>
+      </c>
+      <c r="C81" t="s">
+        <v>272</v>
+      </c>
+      <c r="D81" t="s">
+        <v>273</v>
+      </c>
+      <c r="E81" t="s">
+        <v>274</v>
+      </c>
+      <c r="F81" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H81" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.162950069858618</v>
+      </c>
+      <c r="J81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L81" t="s">
+        <v>275</v>
+      </c>
+      <c r="M81" t="s">
+        <v>276</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-30.676</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.51976084243896</v>
+      </c>
+      <c r="P81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R81" s="11" t="n">
+        <v>27.7374308380844</v>
+      </c>
+      <c r="S81" t="n">
+        <v>3</v>
+      </c>
+      <c r="T81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V81" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH81" t="s">
+        <v>480</v>
+      </c>
+      <c r="AI81" t="s">
+        <v>481</v>
+      </c>
+      <c r="AJ81" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="82" ht="19" customHeight="1">
-      <c r="R82" s="11"/>
-      <c r="V82" s="11"/>
+      <c r="A82" t="s">
+        <v>482</v>
+      </c>
+      <c r="B82" t="s">
+        <v>271</v>
+      </c>
+      <c r="C82" t="s">
+        <v>272</v>
+      </c>
+      <c r="D82" t="s">
+        <v>273</v>
+      </c>
+      <c r="E82" t="s">
+        <v>274</v>
+      </c>
+      <c r="F82" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H82" t="n">
+        <v>34.69</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.167532785535864</v>
+      </c>
+      <c r="J82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L82" t="s">
+        <v>275</v>
+      </c>
+      <c r="M82" t="s">
+        <v>276</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-31.327</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.39999999999925</v>
+      </c>
+      <c r="P82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R82" s="11" t="n">
+        <v>28.7716082387042</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V82" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH82" t="s">
+        <v>483</v>
+      </c>
+      <c r="AI82" t="s">
+        <v>484</v>
+      </c>
+      <c r="AJ82" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="83" ht="19" customHeight="1">
-      <c r="R83" s="11"/>
-      <c r="V83" s="11"/>
+      <c r="A83" t="s">
+        <v>485</v>
+      </c>
+      <c r="B83" t="s">
+        <v>271</v>
+      </c>
+      <c r="C83" t="s">
+        <v>272</v>
+      </c>
+      <c r="D83" t="s">
+        <v>273</v>
+      </c>
+      <c r="E83" t="s">
+        <v>274</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H83" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.170279119117668</v>
+      </c>
+      <c r="J83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L83" t="s">
+        <v>275</v>
+      </c>
+      <c r="M83" t="s">
+        <v>276</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-30.5805</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.234999999999999</v>
+      </c>
+      <c r="P83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R83" s="11" t="n">
+        <v>28.0920934134022</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V83" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH83" t="s">
+        <v>486</v>
+      </c>
+      <c r="AI83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ83" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="84" ht="19" customHeight="1">
-      <c r="R84" s="11"/>
-      <c r="V84" s="11"/>
+      <c r="A84" t="s">
+        <v>487</v>
+      </c>
+      <c r="B84" t="s">
+        <v>271</v>
+      </c>
+      <c r="C84" t="s">
+        <v>272</v>
+      </c>
+      <c r="D84" t="s">
+        <v>273</v>
+      </c>
+      <c r="E84" t="s">
+        <v>274</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H84" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.171514177859809</v>
+      </c>
+      <c r="J84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L84" t="s">
+        <v>275</v>
+      </c>
+      <c r="M84" t="s">
+        <v>276</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-30.65975</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.348063930909311</v>
+      </c>
+      <c r="P84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R84" s="11" t="n">
+        <v>29.3513235936672</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V84" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH84" t="s">
+        <v>488</v>
+      </c>
+      <c r="AI84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ84" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="85" ht="19" customHeight="1">
-      <c r="R85" s="11"/>
-      <c r="V85" s="11"/>
+      <c r="A85" t="s">
+        <v>489</v>
+      </c>
+      <c r="B85" t="s">
+        <v>271</v>
+      </c>
+      <c r="C85" t="s">
+        <v>272</v>
+      </c>
+      <c r="D85" t="s">
+        <v>273</v>
+      </c>
+      <c r="E85" t="s">
+        <v>274</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H85" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.172885895909823</v>
+      </c>
+      <c r="J85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L85" t="s">
+        <v>275</v>
+      </c>
+      <c r="M85" t="s">
+        <v>276</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-30.83675</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.21644822321593</v>
+      </c>
+      <c r="P85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R85" s="11" t="n">
+        <v>28.7325325189738</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V85" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH85" t="s">
+        <v>490</v>
+      </c>
+      <c r="AI85" t="s">
+        <v>491</v>
+      </c>
+      <c r="AJ85" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="86" ht="19" customHeight="1">
-      <c r="R86" s="11"/>
-      <c r="V86" s="11"/>
+      <c r="A86" t="s">
+        <v>492</v>
+      </c>
+      <c r="B86" t="s">
+        <v>271</v>
+      </c>
+      <c r="C86" t="s">
+        <v>272</v>
+      </c>
+      <c r="D86" t="s">
+        <v>273</v>
+      </c>
+      <c r="E86" t="s">
+        <v>274</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H86" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.173937143656966</v>
+      </c>
+      <c r="J86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L86" t="s">
+        <v>275</v>
+      </c>
+      <c r="M86" t="s">
+        <v>276</v>
+      </c>
+      <c r="N86" t="n">
+        <v>-31.2705</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.466837587746407</v>
+      </c>
+      <c r="P86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R86" s="11" t="n">
+        <v>29.162546564548</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V86" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH86" t="s">
+        <v>493</v>
+      </c>
+      <c r="AI86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ86" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="87" ht="19" customHeight="1">
-      <c r="R87" s="11"/>
-      <c r="V87" s="11"/>
+      <c r="A87" t="s">
+        <v>494</v>
+      </c>
+      <c r="B87" t="s">
+        <v>271</v>
+      </c>
+      <c r="C87" t="s">
+        <v>272</v>
+      </c>
+      <c r="D87" t="s">
+        <v>273</v>
+      </c>
+      <c r="E87" t="s">
+        <v>274</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H87" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.175718902402213</v>
+      </c>
+      <c r="J87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L87" t="s">
+        <v>275</v>
+      </c>
+      <c r="M87" t="s">
+        <v>276</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-33.27375</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.63053667617369</v>
+      </c>
+      <c r="P87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R87" s="11" t="n">
+        <v>28.5231783075396</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V87" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH87" t="s">
+        <v>495</v>
+      </c>
+      <c r="AI87" t="s">
+        <v>496</v>
+      </c>
+      <c r="AJ87" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="88" ht="19" customHeight="1">
-      <c r="R88" s="11"/>
-      <c r="V88" s="11"/>
+      <c r="A88" t="s">
+        <v>497</v>
+      </c>
+      <c r="B88" t="s">
+        <v>271</v>
+      </c>
+      <c r="C88" t="s">
+        <v>272</v>
+      </c>
+      <c r="D88" t="s">
+        <v>273</v>
+      </c>
+      <c r="E88" t="s">
+        <v>274</v>
+      </c>
+      <c r="F88" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H88" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.177225773490679</v>
+      </c>
+      <c r="J88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L88" t="s">
+        <v>275</v>
+      </c>
+      <c r="M88" t="s">
+        <v>276</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-31.252</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.138193101612683</v>
+      </c>
+      <c r="P88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R88" s="11" t="n">
+        <v>30.1508732414292</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V88" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH88" t="s">
+        <v>498</v>
+      </c>
+      <c r="AI88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ88" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="89" ht="19" customHeight="1">
-      <c r="R89" s="11"/>
-      <c r="V89" s="11"/>
+      <c r="A89" t="s">
+        <v>499</v>
+      </c>
+      <c r="B89" t="s">
+        <v>271</v>
+      </c>
+      <c r="C89" t="s">
+        <v>272</v>
+      </c>
+      <c r="D89" t="s">
+        <v>273</v>
+      </c>
+      <c r="E89" t="s">
+        <v>274</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G89" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H89" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.178549415767186</v>
+      </c>
+      <c r="J89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L89" t="s">
+        <v>275</v>
+      </c>
+      <c r="M89" t="s">
+        <v>276</v>
+      </c>
+      <c r="N89" t="n">
+        <v>-30.558</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.689999999999569</v>
+      </c>
+      <c r="P89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R89" s="11" t="n">
+        <v>28.5587205258649</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V89" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH89" t="s">
+        <v>500</v>
+      </c>
+      <c r="AI89" t="s">
+        <v>501</v>
+      </c>
+      <c r="AJ89" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="90" ht="19" customHeight="1">
-      <c r="R90" s="11"/>
-      <c r="V90" s="11"/>
+      <c r="A90" t="s">
+        <v>502</v>
+      </c>
+      <c r="B90" t="s">
+        <v>271</v>
+      </c>
+      <c r="C90" t="s">
+        <v>272</v>
+      </c>
+      <c r="D90" t="s">
+        <v>273</v>
+      </c>
+      <c r="E90" t="s">
+        <v>274</v>
+      </c>
+      <c r="F90" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H90" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.18005497782788</v>
+      </c>
+      <c r="J90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L90" t="s">
+        <v>275</v>
+      </c>
+      <c r="M90" t="s">
+        <v>276</v>
+      </c>
+      <c r="N90" t="n">
+        <v>-30.868</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.115542200082913</v>
+      </c>
+      <c r="P90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R90" s="11" t="n">
+        <v>28.9536255117351</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V90" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH90" t="s">
+        <v>503</v>
+      </c>
+      <c r="AI90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ90" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="91" ht="19" customHeight="1">
-      <c r="R91" s="11"/>
-      <c r="V91" s="11"/>
+      <c r="A91" t="s">
+        <v>504</v>
+      </c>
+      <c r="B91" t="s">
+        <v>271</v>
+      </c>
+      <c r="C91" t="s">
+        <v>272</v>
+      </c>
+      <c r="D91" t="s">
+        <v>273</v>
+      </c>
+      <c r="E91" t="s">
+        <v>274</v>
+      </c>
+      <c r="F91" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H91" t="n">
+        <v>38.55</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.185159675825315</v>
+      </c>
+      <c r="J91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L91" t="s">
+        <v>275</v>
+      </c>
+      <c r="M91" t="s">
+        <v>276</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-30.64725</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.422597326068129</v>
+      </c>
+      <c r="P91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R91" s="11" t="n">
+        <v>29.7253738709977</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V91" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH91" t="s">
+        <v>505</v>
+      </c>
+      <c r="AI91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ91" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="92" ht="19" customHeight="1">
-      <c r="R92" s="11"/>
-      <c r="V92" s="11"/>
+      <c r="A92" t="s">
+        <v>506</v>
+      </c>
+      <c r="B92" t="s">
+        <v>271</v>
+      </c>
+      <c r="C92" t="s">
+        <v>272</v>
+      </c>
+      <c r="D92" t="s">
+        <v>273</v>
+      </c>
+      <c r="E92" t="s">
+        <v>274</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G92" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H92" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.183793108599682</v>
+      </c>
+      <c r="J92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L92" t="s">
+        <v>275</v>
+      </c>
+      <c r="M92" t="s">
+        <v>276</v>
+      </c>
+      <c r="N92" t="n">
+        <v>-30.22775</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.497085338078844</v>
+      </c>
+      <c r="P92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R92" s="11" t="n">
+        <v>28.6176606397799</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V92" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA92" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH92" t="s">
+        <v>507</v>
+      </c>
+      <c r="AI92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ92" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="93" ht="19" customHeight="1">
-      <c r="R93" s="11"/>
-      <c r="V93" s="11"/>
+      <c r="A93" t="s">
+        <v>508</v>
+      </c>
+      <c r="B93" t="s">
+        <v>271</v>
+      </c>
+      <c r="C93" t="s">
+        <v>272</v>
+      </c>
+      <c r="D93" t="s">
+        <v>273</v>
+      </c>
+      <c r="E93" t="s">
+        <v>274</v>
+      </c>
+      <c r="F93" t="n">
+        <v>4.20416666666667</v>
+      </c>
+      <c r="G93" t="n">
+        <v>-43.4888333333333</v>
+      </c>
+      <c r="H93" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.185478462095203</v>
+      </c>
+      <c r="J93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L93" t="s">
+        <v>275</v>
+      </c>
+      <c r="M93" t="s">
+        <v>276</v>
+      </c>
+      <c r="N93" t="n">
+        <v>-30.128</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.808991965349301</v>
+      </c>
+      <c r="P93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R93" s="11" t="n">
+        <v>30.4774280816219</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5.22015325445528</v>
+      </c>
+      <c r="T93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V93" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA93" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>5.661324</v>
+      </c>
+      <c r="AC93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>2.75970332407639</v>
+      </c>
+      <c r="AG93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH93" t="s">
+        <v>509</v>
+      </c>
+      <c r="AI93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ93" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="94" ht="19" customHeight="1">
       <c r="R94" s="11"/>
@@ -9526,67 +13023,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-    <hyperlink ref="C52" r:id="rId48h"/>
-    <hyperlink ref="C53" r:id="rId49h"/>
-    <hyperlink ref="C54" r:id="rId50h"/>
-    <hyperlink ref="C55" r:id="rId51h"/>
-    <hyperlink ref="C56" r:id="rId52h"/>
-    <hyperlink ref="C57" r:id="rId53h"/>
-    <hyperlink ref="C58" r:id="rId54h"/>
-    <hyperlink ref="C59" r:id="rId55h"/>
-    <hyperlink ref="C60" r:id="rId56h"/>
-    <hyperlink ref="C61" r:id="rId57h"/>
-    <hyperlink ref="C62" r:id="rId58h"/>
-    <hyperlink ref="C63" r:id="rId59h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
